--- a/predictions.xlsx
+++ b/predictions.xlsx
@@ -440,7 +440,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.837998509407043</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.4954972267150879</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.05328812822699547</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0.1503237783908844</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.2086868286132812</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-1.122004628181458</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0.970087468624115</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.3994841575622559</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-1.258513331413269</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17.12261962890625</v>
+        <v>3.04087233543396</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.03579330444336</v>
+        <v>16.15715980529785</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.16177368164062</v>
+        <v>53.23015213012695</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>58.62170791625977</v>
+        <v>77.26535797119141</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40.97102737426758</v>
+        <v>78.54056549072266</v>
       </c>
     </row>
     <row r="16">
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>54.65586853027344</v>
+        <v>70.32315063476562</v>
       </c>
     </row>
     <row r="17">
@@ -560,7 +560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>55.59368515014648</v>
+        <v>57.85924911499023</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>64.29643249511719</v>
+        <v>62.79743194580078</v>
       </c>
     </row>
     <row r="19">
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>59.23862457275391</v>
+        <v>84.12172698974609</v>
       </c>
     </row>
     <row r="20">
@@ -584,7 +584,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.81834411621094</v>
+        <v>90.74658203125</v>
       </c>
     </row>
     <row r="21">
@@ -592,7 +592,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>42.9115104675293</v>
+        <v>35.36873626708984</v>
       </c>
     </row>
     <row r="22">
@@ -600,7 +600,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>17.23799324035645</v>
+        <v>14.32930660247803</v>
       </c>
     </row>
     <row r="23">
@@ -608,7 +608,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>7.44691276550293</v>
       </c>
     </row>
     <row r="24">
@@ -616,7 +616,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>7.174227237701416</v>
+        <v>5.744593620300293</v>
       </c>
     </row>
     <row r="25">
@@ -624,7 +624,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>2.969736099243164</v>
+        <v>1.505883693695068</v>
       </c>
     </row>
     <row r="26">
@@ -632,7 +632,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2.307127952575684</v>
+        <v>-0.2787218987941742</v>
       </c>
     </row>
     <row r="27">
@@ -640,7 +640,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>6.738043308258057</v>
+        <v>0.4111593961715698</v>
       </c>
     </row>
     <row r="28">
@@ -648,7 +648,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2.852198839187622</v>
+        <v>0.6929543614387512</v>
       </c>
     </row>
     <row r="29">
@@ -656,7 +656,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.734227180480957</v>
       </c>
     </row>
     <row r="30">
@@ -664,7 +664,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1.150508165359497</v>
       </c>
     </row>
     <row r="31">
@@ -672,7 +672,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.3205906748771667</v>
       </c>
     </row>
     <row r="32">
@@ -680,7 +680,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.2705534100532532</v>
       </c>
     </row>
     <row r="33">
@@ -688,7 +688,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2.008792161941528</v>
+        <v>1.194918632507324</v>
       </c>
     </row>
     <row r="34">
@@ -696,7 +696,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>6.583968162536621</v>
+        <v>2.096201181411743</v>
       </c>
     </row>
     <row r="35">
@@ -704,7 +704,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>5.374340534210205</v>
+        <v>8.071408271789551</v>
       </c>
     </row>
     <row r="36">
@@ -712,7 +712,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>27.61741828918457</v>
+        <v>33.09955215454102</v>
       </c>
     </row>
     <row r="37">
@@ -720,7 +720,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>28.57328224182129</v>
+        <v>64.76436614990234</v>
       </c>
     </row>
     <row r="38">
@@ -728,7 +728,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>79.00895690917969</v>
+        <v>92.63680267333984</v>
       </c>
     </row>
     <row r="39">
@@ -736,7 +736,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>102.9099273681641</v>
+        <v>88.36651611328125</v>
       </c>
     </row>
     <row r="40">
@@ -744,7 +744,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>110.902229309082</v>
+        <v>90.01531982421875</v>
       </c>
     </row>
     <row r="41">
@@ -752,7 +752,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>97.19298553466797</v>
+        <v>104.0205535888672</v>
       </c>
     </row>
     <row r="42">
@@ -760,7 +760,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>84.23291778564453</v>
+        <v>83.86949157714844</v>
       </c>
     </row>
     <row r="43">
@@ -768,7 +768,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>81.74640655517578</v>
+        <v>92.40605163574219</v>
       </c>
     </row>
     <row r="44">
@@ -776,7 +776,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>71.63706970214844</v>
+        <v>81.95431518554688</v>
       </c>
     </row>
     <row r="45">
@@ -784,7 +784,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>45.01869964599609</v>
+        <v>41.25622177124023</v>
       </c>
     </row>
     <row r="46">
@@ -792,7 +792,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>15.34609031677246</v>
+        <v>18.13549995422363</v>
       </c>
     </row>
     <row r="47">
@@ -800,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>6.848808765411377</v>
+        <v>1.960195899009705</v>
       </c>
     </row>
     <row r="48">
@@ -808,7 +808,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>3.306149482727051</v>
+        <v>6.153698444366455</v>
       </c>
     </row>
     <row r="49">
@@ -816,7 +816,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>2.072372436523438</v>
+        <v>7.441833972930908</v>
       </c>
     </row>
     <row r="50">
@@ -824,7 +824,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4.509529590606689</v>
+        <v>-0.3874869644641876</v>
       </c>
     </row>
     <row r="51">
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>0.3643567264080048</v>
       </c>
     </row>
     <row r="52">
@@ -840,7 +840,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>-0.5398117303848267</v>
       </c>
     </row>
     <row r="53">
@@ -848,7 +848,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>2.06395697593689</v>
+        <v>-0.2201289534568787</v>
       </c>
     </row>
     <row r="54">
@@ -856,7 +856,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>-0.197330504655838</v>
       </c>
     </row>
     <row r="55">
@@ -864,7 +864,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>-1.003469467163086</v>
       </c>
     </row>
     <row r="56">
@@ -872,7 +872,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>0.4178679287433624</v>
       </c>
     </row>
     <row r="57">
@@ -880,7 +880,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>-0.61417555809021</v>
       </c>
     </row>
     <row r="58">
@@ -888,7 +888,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>0.1208003684878349</v>
       </c>
     </row>
     <row r="59">
@@ -896,7 +896,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>10.23027324676514</v>
+        <v>1.088971734046936</v>
       </c>
     </row>
     <row r="60">
@@ -904,7 +904,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>33.68579483032227</v>
+        <v>28.73237800598145</v>
       </c>
     </row>
     <row r="61">
@@ -912,7 +912,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>64.80525207519531</v>
+        <v>66.29437255859375</v>
       </c>
     </row>
     <row r="62">
@@ -920,7 +920,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>112.6763229370117</v>
+        <v>100.4659652709961</v>
       </c>
     </row>
     <row r="63">
@@ -928,7 +928,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>107.7754211425781</v>
+        <v>104.9016647338867</v>
       </c>
     </row>
     <row r="64">
@@ -936,7 +936,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>115.3886032104492</v>
+        <v>109.5033416748047</v>
       </c>
     </row>
     <row r="65">
@@ -944,7 +944,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>114.6721954345703</v>
+        <v>92.04682922363281</v>
       </c>
     </row>
     <row r="66">
@@ -952,7 +952,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>73.71096038818359</v>
+        <v>60.35604858398438</v>
       </c>
     </row>
     <row r="67">
@@ -960,7 +960,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>55.93898391723633</v>
+        <v>85.90196228027344</v>
       </c>
     </row>
     <row r="68">
@@ -968,7 +968,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>80.5565185546875</v>
+        <v>89.25115966796875</v>
       </c>
     </row>
     <row r="69">
@@ -976,7 +976,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>38.57832336425781</v>
+        <v>32.31981658935547</v>
       </c>
     </row>
     <row r="70">
@@ -984,7 +984,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>16.2238941192627</v>
+        <v>17.67133331298828</v>
       </c>
     </row>
     <row r="71">
@@ -992,7 +992,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>6.30801248550415</v>
+        <v>10.17463397979736</v>
       </c>
     </row>
     <row r="72">
@@ -1000,7 +1000,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>8.475473403930664</v>
+        <v>6.849337577819824</v>
       </c>
     </row>
     <row r="73">
@@ -1008,7 +1008,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>11.91022109985352</v>
+        <v>5.628532886505127</v>
       </c>
     </row>
     <row r="74">
@@ -1016,7 +1016,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>3.528717756271362</v>
       </c>
     </row>
     <row r="75">
@@ -1024,7 +1024,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>3.885640621185303</v>
       </c>
     </row>
     <row r="76">
@@ -1032,7 +1032,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>0.4169952571392059</v>
       </c>
     </row>
     <row r="77">
@@ -1040,7 +1040,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>0.1665710806846619</v>
       </c>
     </row>
     <row r="78">
@@ -1048,7 +1048,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>-0.3559686541557312</v>
       </c>
     </row>
     <row r="79">
@@ -1056,7 +1056,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>-0.4553071856498718</v>
       </c>
     </row>
     <row r="80">
@@ -1064,7 +1064,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>-0.8475037813186646</v>
       </c>
     </row>
     <row r="81">
@@ -1072,7 +1072,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>-0.1764041483402252</v>
       </c>
     </row>
     <row r="82">
@@ -1080,7 +1080,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-3.677674770355225</v>
       </c>
     </row>
     <row r="83">
@@ -1088,7 +1088,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>2.618813991546631</v>
       </c>
     </row>
     <row r="84">
@@ -1096,7 +1096,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>17.89366149902344</v>
+        <v>21.04161262512207</v>
       </c>
     </row>
     <row r="85">
@@ -1104,7 +1104,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>51.88057708740234</v>
+        <v>43.96057891845703</v>
       </c>
     </row>
     <row r="86">
@@ -1112,7 +1112,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>60.28753662109375</v>
+        <v>47.3422966003418</v>
       </c>
     </row>
     <row r="87">
@@ -1120,7 +1120,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>92.16204071044922</v>
+        <v>41.95147705078125</v>
       </c>
     </row>
     <row r="88">
@@ -1128,7 +1128,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>86.94500732421875</v>
+        <v>65.55846405029297</v>
       </c>
     </row>
     <row r="89">
@@ -1136,7 +1136,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>88.98038482666016</v>
+        <v>62.51725006103516</v>
       </c>
     </row>
     <row r="90">
@@ -1144,7 +1144,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>83.18907165527344</v>
+        <v>34.92081069946289</v>
       </c>
     </row>
     <row r="91">
@@ -1152,7 +1152,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>89.82496643066406</v>
+        <v>54.62783050537109</v>
       </c>
     </row>
     <row r="92">
@@ -1160,7 +1160,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>80.03872680664062</v>
+        <v>41.54820251464844</v>
       </c>
     </row>
     <row r="93">
@@ -1168,7 +1168,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>48.6728515625</v>
+        <v>28.20265007019043</v>
       </c>
     </row>
     <row r="94">
@@ -1176,7 +1176,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>12.05544662475586</v>
+        <v>9.333469390869141</v>
       </c>
     </row>
     <row r="95">
@@ -1184,7 +1184,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>2.630396604537964</v>
       </c>
     </row>
     <row r="96">
@@ -1192,7 +1192,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.9142712354660034</v>
       </c>
     </row>
     <row r="97">
@@ -1200,7 +1200,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.5373373627662659</v>
       </c>
     </row>
     <row r="98">
@@ -1208,7 +1208,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>-0.03420323878526688</v>
       </c>
     </row>
     <row r="99">
@@ -1216,7 +1216,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>-0.3115522563457489</v>
       </c>
     </row>
     <row r="100">
@@ -1224,7 +1224,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>-0.4589079618453979</v>
       </c>
     </row>
     <row r="101">
@@ -1232,7 +1232,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>-0.1337208449840546</v>
       </c>
     </row>
     <row r="102">
@@ -1240,7 +1240,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>-0.6111610531806946</v>
       </c>
     </row>
     <row r="103">
@@ -1248,7 +1248,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>-0.5894138216972351</v>
       </c>
     </row>
     <row r="104">
@@ -1256,7 +1256,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>-0.6406461000442505</v>
       </c>
     </row>
     <row r="105">
@@ -1264,7 +1264,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>0.1894106864929199</v>
       </c>
     </row>
     <row r="106">
@@ -1272,7 +1272,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>0.2322503924369812</v>
       </c>
     </row>
     <row r="107">
@@ -1280,7 +1280,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>6.037909030914307</v>
+        <v>8.126225471496582</v>
       </c>
     </row>
     <row r="108">
@@ -1288,7 +1288,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>28.42985916137695</v>
+        <v>26.87890243530273</v>
       </c>
     </row>
     <row r="109">
@@ -1296,7 +1296,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>69.47907257080078</v>
+        <v>53.92345809936523</v>
       </c>
     </row>
     <row r="110">
@@ -1304,7 +1304,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>90.41035461425781</v>
+        <v>81.87494659423828</v>
       </c>
     </row>
     <row r="111">
@@ -1312,7 +1312,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>91.27116394042969</v>
+        <v>119.9293975830078</v>
       </c>
     </row>
     <row r="112">
@@ -1320,7 +1320,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>110.4103240966797</v>
+        <v>114.246826171875</v>
       </c>
     </row>
     <row r="113">
@@ -1328,7 +1328,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>82.67634582519531</v>
+        <v>108.1624984741211</v>
       </c>
     </row>
     <row r="114">
@@ -1336,7 +1336,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>83.4378662109375</v>
+        <v>63.95932769775391</v>
       </c>
     </row>
     <row r="115">
@@ -1344,7 +1344,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>108.0868453979492</v>
+        <v>87.92794036865234</v>
       </c>
     </row>
     <row r="116">
@@ -1352,7 +1352,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>64.97136688232422</v>
+        <v>70.02020263671875</v>
       </c>
     </row>
     <row r="117">
@@ -1360,7 +1360,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>26.0109748840332</v>
+        <v>27.958251953125</v>
       </c>
     </row>
     <row r="118">
@@ -1368,7 +1368,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>15.8126974105835</v>
+        <v>8.139360427856445</v>
       </c>
     </row>
     <row r="119">
@@ -1376,7 +1376,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>5.144100189208984</v>
+        <v>-4.704663753509521</v>
       </c>
     </row>
     <row r="120">
@@ -1384,7 +1384,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>6.640934467315674</v>
+        <v>-5.057145595550537</v>
       </c>
     </row>
     <row r="121">
@@ -1392,7 +1392,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>7.888374805450439</v>
+        <v>-3.280220985412598</v>
       </c>
     </row>
     <row r="122">
@@ -1400,7 +1400,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>3.766584634780884</v>
+        <v>-4.565710544586182</v>
       </c>
     </row>
     <row r="123">
@@ -1408,7 +1408,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>2.130186080932617</v>
+        <v>-3.644694328308105</v>
       </c>
     </row>
     <row r="124">
@@ -1416,7 +1416,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>-4.129497051239014</v>
       </c>
     </row>
     <row r="125">
@@ -1424,7 +1424,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>-4.111227989196777</v>
       </c>
     </row>
     <row r="126">
@@ -1432,7 +1432,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>1.157152056694031</v>
       </c>
     </row>
     <row r="127">
@@ -1440,7 +1440,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>0.7589803338050842</v>
       </c>
     </row>
     <row r="128">
@@ -1448,7 +1448,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-4.639681816101074</v>
       </c>
     </row>
     <row r="129">
@@ -1456,7 +1456,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>9.115219116210938</v>
+        <v>2.245379686355591</v>
       </c>
     </row>
     <row r="130">
@@ -1464,7 +1464,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>6.066996574401855</v>
       </c>
     </row>
     <row r="131">
@@ -1472,7 +1472,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>8.883520126342773</v>
+        <v>4.00863790512085</v>
       </c>
     </row>
     <row r="132">
@@ -1480,7 +1480,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>29.69071960449219</v>
+        <v>9.082454681396484</v>
       </c>
     </row>
     <row r="133">
@@ -1488,7 +1488,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>46.52538299560547</v>
+        <v>24.03257179260254</v>
       </c>
     </row>
     <row r="134">
@@ -1496,7 +1496,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>43.69960021972656</v>
+        <v>28.74856948852539</v>
       </c>
     </row>
     <row r="135">
@@ -1504,7 +1504,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>79.60040283203125</v>
+        <v>87.70124816894531</v>
       </c>
     </row>
     <row r="136">
@@ -1512,7 +1512,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>107.4008178710938</v>
+        <v>112.9677963256836</v>
       </c>
     </row>
     <row r="137">
@@ -1520,7 +1520,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>96.18132781982422</v>
+        <v>91.76232147216797</v>
       </c>
     </row>
     <row r="138">
@@ -1528,7 +1528,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>76.97018432617188</v>
+        <v>90.05353546142578</v>
       </c>
     </row>
     <row r="139">
@@ -1536,7 +1536,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>100.1797943115234</v>
+        <v>65.41109466552734</v>
       </c>
     </row>
     <row r="140">
@@ -1544,7 +1544,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>64.90351867675781</v>
+        <v>64.69100952148438</v>
       </c>
     </row>
     <row r="141">
@@ -1552,7 +1552,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>18.23526573181152</v>
+        <v>28.18703842163086</v>
       </c>
     </row>
     <row r="142">
@@ -1560,7 +1560,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>7.636003494262695</v>
+        <v>8.892467498779297</v>
       </c>
     </row>
     <row r="143">
@@ -1568,7 +1568,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>-2.271406888961792</v>
       </c>
     </row>
     <row r="144">
@@ -1576,7 +1576,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>-0.1187590584158897</v>
       </c>
     </row>
     <row r="145">
@@ -1584,7 +1584,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>-2.739768743515015</v>
       </c>
     </row>
     <row r="146">
@@ -1592,7 +1592,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>-2.547905206680298</v>
       </c>
     </row>
     <row r="147">
@@ -1600,7 +1600,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>-2.449855089187622</v>
       </c>
     </row>
     <row r="148">
@@ -1608,7 +1608,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>-4.532144546508789</v>
       </c>
     </row>
     <row r="149">
@@ -1616,7 +1616,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>-7.822174549102783</v>
       </c>
     </row>
     <row r="150">
@@ -1624,7 +1624,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>-7.293653011322021</v>
       </c>
     </row>
     <row r="151">
@@ -1632,7 +1632,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>-4.571131229400635</v>
       </c>
     </row>
     <row r="152">
@@ -1640,7 +1640,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>-3.386038780212402</v>
       </c>
     </row>
     <row r="153">
@@ -1648,7 +1648,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>2.857801914215088</v>
       </c>
     </row>
     <row r="154">
@@ -1656,7 +1656,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>-0.1089461222290993</v>
       </c>
     </row>
     <row r="155">
@@ -1664,7 +1664,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>7.539859771728516</v>
       </c>
     </row>
     <row r="156">
@@ -1672,7 +1672,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>20.45589828491211</v>
+        <v>27.43085670471191</v>
       </c>
     </row>
     <row r="157">
@@ -1680,7 +1680,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>26.34695243835449</v>
+        <v>21.24585914611816</v>
       </c>
     </row>
     <row r="158">
@@ -1688,7 +1688,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>26.96721267700195</v>
+        <v>53.12742233276367</v>
       </c>
     </row>
     <row r="159">
@@ -1696,7 +1696,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>74.99337005615234</v>
+        <v>89.24996948242188</v>
       </c>
     </row>
     <row r="160">
@@ -1704,7 +1704,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>84.20703887939453</v>
+        <v>88.73116302490234</v>
       </c>
     </row>
     <row r="161">
@@ -1712,7 +1712,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>82.67136383056641</v>
+        <v>74.11979675292969</v>
       </c>
     </row>
     <row r="162">
@@ -1720,7 +1720,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>80.01935577392578</v>
+        <v>64.36436462402344</v>
       </c>
     </row>
     <row r="163">
@@ -1728,7 +1728,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>71.06666564941406</v>
+        <v>67.58683776855469</v>
       </c>
     </row>
     <row r="164">
@@ -1736,7 +1736,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>50.13944244384766</v>
+        <v>53.7429084777832</v>
       </c>
     </row>
     <row r="165">
@@ -1744,7 +1744,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>21.81836318969727</v>
+        <v>24.96453857421875</v>
       </c>
     </row>
     <row r="166">
@@ -1752,7 +1752,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>9.895528793334961</v>
+        <v>10.7595329284668</v>
       </c>
     </row>
     <row r="167">
@@ -1760,7 +1760,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>1.405218720436096</v>
       </c>
     </row>
     <row r="168">
@@ -1768,7 +1768,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>2.880450963973999</v>
+        <v>1.487916111946106</v>
       </c>
     </row>
     <row r="169">
@@ -1776,7 +1776,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>1.486667513847351</v>
       </c>
     </row>
     <row r="170">
@@ -1784,7 +1784,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>-0.02072453312575817</v>
       </c>
     </row>
     <row r="171">
@@ -1792,7 +1792,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>-0.04021257534623146</v>
       </c>
     </row>
     <row r="172">
@@ -1800,7 +1800,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>-0.899152398109436</v>
       </c>
     </row>
     <row r="173">
@@ -1808,7 +1808,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.06221381947398186</v>
       </c>
     </row>
     <row r="174">
@@ -1816,7 +1816,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>0.09754638373851776</v>
       </c>
     </row>
     <row r="175">
@@ -1824,7 +1824,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>-0.1749149858951569</v>
       </c>
     </row>
     <row r="176">
@@ -1832,7 +1832,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>0.1332631409168243</v>
       </c>
     </row>
     <row r="177">
@@ -1840,7 +1840,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>-1.709261178970337</v>
       </c>
     </row>
     <row r="178">
@@ -1848,7 +1848,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>4.144211292266846</v>
+        <v>1.433374404907227</v>
       </c>
     </row>
     <row r="179">
@@ -1856,7 +1856,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>7.170076847076416</v>
+        <v>16.40782928466797</v>
       </c>
     </row>
     <row r="180">
@@ -1864,7 +1864,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>31.05545616149902</v>
+        <v>36.91202163696289</v>
       </c>
     </row>
     <row r="181">
@@ -1872,7 +1872,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>61.06442642211914</v>
+        <v>71.498046875</v>
       </c>
     </row>
     <row r="182">
@@ -1880,7 +1880,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>93.56131744384766</v>
+        <v>94.45830535888672</v>
       </c>
     </row>
     <row r="183">
@@ -1888,7 +1888,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>122.8619384765625</v>
+        <v>123.9582290649414</v>
       </c>
     </row>
     <row r="184">
@@ -1896,7 +1896,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>128.8665313720703</v>
+        <v>137.2661590576172</v>
       </c>
     </row>
     <row r="185">
@@ -1904,7 +1904,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>128.3878173828125</v>
+        <v>127.0240936279297</v>
       </c>
     </row>
     <row r="186">
@@ -1912,7 +1912,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>114.5887451171875</v>
+        <v>113.1853103637695</v>
       </c>
     </row>
     <row r="187">
@@ -1920,7 +1920,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>111.9318618774414</v>
+        <v>81.66146850585938</v>
       </c>
     </row>
     <row r="188">
@@ -1928,7 +1928,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>84.51595306396484</v>
+        <v>63.86695098876953</v>
       </c>
     </row>
     <row r="189">
@@ -1936,7 +1936,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>24.27577209472656</v>
+        <v>27.19776344299316</v>
       </c>
     </row>
     <row r="190">
@@ -1944,7 +1944,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>14.49163818359375</v>
+        <v>11.14963912963867</v>
       </c>
     </row>
     <row r="191">
@@ -1952,7 +1952,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>2.228377819061279</v>
+        <v>0.3209110498428345</v>
       </c>
     </row>
     <row r="192">
@@ -1960,7 +1960,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>2.047730684280396</v>
+        <v>1.017351984977722</v>
       </c>
     </row>
     <row r="193">
@@ -1968,7 +1968,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>1.752984881401062</v>
       </c>
     </row>
     <row r="194">
@@ -1976,7 +1976,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>0.8184607625007629</v>
       </c>
     </row>
     <row r="195">
@@ -1984,7 +1984,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>0.2865709960460663</v>
       </c>
     </row>
     <row r="196">
@@ -1992,7 +1992,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>-0.2928558886051178</v>
       </c>
     </row>
     <row r="197">
@@ -2000,7 +2000,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>-0.5491536855697632</v>
       </c>
     </row>
     <row r="198">
@@ -2008,7 +2008,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>-0.4146327674388885</v>
       </c>
     </row>
     <row r="199">
@@ -2016,7 +2016,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>-0.4759921729564667</v>
       </c>
     </row>
     <row r="200">
@@ -2024,7 +2024,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>-0.8326437473297119</v>
       </c>
     </row>
     <row r="201">
@@ -2032,7 +2032,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>-0.8198114633560181</v>
       </c>
     </row>
     <row r="202">
@@ -2040,7 +2040,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>5.324351787567139</v>
+        <v>-0.9359853267669678</v>
       </c>
     </row>
     <row r="203">
@@ -2048,7 +2048,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>7.583852767944336</v>
+        <v>4.707770824432373</v>
       </c>
     </row>
     <row r="204">
@@ -2056,7 +2056,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>32.2319450378418</v>
+        <v>35.38999557495117</v>
       </c>
     </row>
     <row r="205">
@@ -2064,7 +2064,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>62.21095275878906</v>
+        <v>53.73974990844727</v>
       </c>
     </row>
     <row r="206">
@@ -2072,7 +2072,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>73.48064422607422</v>
+        <v>87.85048675537109</v>
       </c>
     </row>
     <row r="207">
@@ -2080,7 +2080,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>114.5502243041992</v>
+        <v>116.7160949707031</v>
       </c>
     </row>
     <row r="208">
@@ -2088,7 +2088,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>113.626579284668</v>
+        <v>130.3075561523438</v>
       </c>
     </row>
     <row r="209">
@@ -2096,7 +2096,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>105.3620147705078</v>
+        <v>113.3037185668945</v>
       </c>
     </row>
     <row r="210">
@@ -2104,7 +2104,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>102.8899002075195</v>
+        <v>111.3520965576172</v>
       </c>
     </row>
     <row r="211">
@@ -2112,7 +2112,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>76.40805053710938</v>
+        <v>106.9210357666016</v>
       </c>
     </row>
     <row r="212">
@@ -2120,7 +2120,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>54.23951721191406</v>
+        <v>82.89585113525391</v>
       </c>
     </row>
     <row r="213">
@@ -2128,7 +2128,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>19.57104301452637</v>
+        <v>23.00207328796387</v>
       </c>
     </row>
     <row r="214">
@@ -2136,7 +2136,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>8.656937599182129</v>
+        <v>13.51536178588867</v>
       </c>
     </row>
     <row r="215">
@@ -2144,7 +2144,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>4.308341979980469</v>
       </c>
     </row>
     <row r="216">
@@ -2152,7 +2152,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>1.563323259353638</v>
       </c>
     </row>
     <row r="217">
@@ -2160,7 +2160,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>2.367169380187988</v>
       </c>
     </row>
     <row r="218">
@@ -2168,7 +2168,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>3.440127372741699</v>
       </c>
     </row>
     <row r="219">
@@ -2176,7 +2176,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>-0.1574985384941101</v>
       </c>
     </row>
     <row r="220">
@@ -2184,7 +2184,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>-0.1547337472438812</v>
       </c>
     </row>
     <row r="221">
@@ -2192,7 +2192,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>0.1856987774372101</v>
       </c>
     </row>
     <row r="222">
@@ -2200,7 +2200,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>0.0845743715763092</v>
       </c>
     </row>
     <row r="223">
@@ -2208,7 +2208,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>-0.1602385342121124</v>
       </c>
     </row>
     <row r="224">
@@ -2216,7 +2216,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>-0.09851273894309998</v>
       </c>
     </row>
     <row r="225">
@@ -2224,7 +2224,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>0.6127294301986694</v>
       </c>
     </row>
     <row r="226">
@@ -2232,7 +2232,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>0.006788607686758041</v>
       </c>
     </row>
     <row r="227">
@@ -2240,7 +2240,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>11.42199230194092</v>
+        <v>8.210811614990234</v>
       </c>
     </row>
     <row r="228">
@@ -2248,7 +2248,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>42.75457000732422</v>
+        <v>34.37289810180664</v>
       </c>
     </row>
     <row r="229">
@@ -2256,7 +2256,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>65.28194427490234</v>
+        <v>70.13334655761719</v>
       </c>
     </row>
     <row r="230">
@@ -2264,7 +2264,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>107.2423477172852</v>
+        <v>92.59325408935547</v>
       </c>
     </row>
     <row r="231">
@@ -2272,7 +2272,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>129.9378509521484</v>
+        <v>133.6701354980469</v>
       </c>
     </row>
     <row r="232">
@@ -2280,7 +2280,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>134.2794494628906</v>
+        <v>126.9721908569336</v>
       </c>
     </row>
     <row r="233">
@@ -2288,7 +2288,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>130.2010040283203</v>
+        <v>115.6374969482422</v>
       </c>
     </row>
     <row r="234">
@@ -2296,7 +2296,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>116.0722274780273</v>
+        <v>91.15929412841797</v>
       </c>
     </row>
     <row r="235">
@@ -2304,7 +2304,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>111.2938842773438</v>
+        <v>102.5730819702148</v>
       </c>
     </row>
     <row r="236">
@@ -2312,7 +2312,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>77.73612213134766</v>
+        <v>79.86559295654297</v>
       </c>
     </row>
     <row r="237">
@@ -2320,7 +2320,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>27.40054130554199</v>
+        <v>27.32252311706543</v>
       </c>
     </row>
     <row r="238">
@@ -2328,7 +2328,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>10.41722011566162</v>
+        <v>13.56420803070068</v>
       </c>
     </row>
     <row r="239">
@@ -2336,7 +2336,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>4.126457214355469</v>
       </c>
     </row>
     <row r="240">
@@ -2344,7 +2344,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>2.933485269546509</v>
       </c>
     </row>
     <row r="241">
@@ -2352,7 +2352,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>6.959650039672852</v>
+        <v>0.4858120381832123</v>
       </c>
     </row>
     <row r="242">
@@ -2360,7 +2360,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>-0.6017756462097168</v>
       </c>
     </row>
     <row r="243">
@@ -2368,7 +2368,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>-0.1425693929195404</v>
       </c>
     </row>
     <row r="244">
@@ -2376,7 +2376,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>0.3486747741699219</v>
       </c>
     </row>
     <row r="245">
@@ -2384,7 +2384,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>0.3486747741699219</v>
       </c>
     </row>
     <row r="246">
@@ -2392,7 +2392,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>0.3589905798435211</v>
       </c>
     </row>
     <row r="247">
@@ -2400,7 +2400,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>0.3032824099063873</v>
       </c>
     </row>
     <row r="248">
@@ -2408,7 +2408,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>0.3242474496364594</v>
       </c>
     </row>
     <row r="249">
@@ -2416,7 +2416,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>0.6454631686210632</v>
       </c>
     </row>
     <row r="250">
@@ -2424,7 +2424,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>0.9639220237731934</v>
       </c>
     </row>
     <row r="251">
@@ -2432,7 +2432,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>4.308006763458252</v>
+        <v>12.64962577819824</v>
       </c>
     </row>
     <row r="252">
@@ -2440,7 +2440,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>39.46875</v>
+        <v>32.44503021240234</v>
       </c>
     </row>
     <row r="253">
@@ -2448,7 +2448,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>89.32664489746094</v>
+        <v>38.55216598510742</v>
       </c>
     </row>
     <row r="254">
@@ -2456,7 +2456,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>95.51340484619141</v>
+        <v>65.49401092529297</v>
       </c>
     </row>
     <row r="255">
@@ -2464,7 +2464,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>124.1354751586914</v>
+        <v>98.02091217041016</v>
       </c>
     </row>
     <row r="256">
@@ -2472,7 +2472,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>101.772575378418</v>
+        <v>90.79268646240234</v>
       </c>
     </row>
     <row r="257">
@@ -2480,7 +2480,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>87.86443328857422</v>
+        <v>102.8112487792969</v>
       </c>
     </row>
     <row r="258">
@@ -2488,7 +2488,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>98.69356536865234</v>
+        <v>94.3792724609375</v>
       </c>
     </row>
     <row r="259">
@@ -2496,7 +2496,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>86.06771850585938</v>
+        <v>75.25985717773438</v>
       </c>
     </row>
     <row r="260">
@@ -2504,7 +2504,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>82.62104034423828</v>
+        <v>68.37284851074219</v>
       </c>
     </row>
     <row r="261">
@@ -2512,7 +2512,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>25.01813888549805</v>
+        <v>20.97550392150879</v>
       </c>
     </row>
     <row r="262">
@@ -2520,7 +2520,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>14.74535655975342</v>
+        <v>9.456229209899902</v>
       </c>
     </row>
     <row r="263">
@@ -2528,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>2.925539493560791</v>
+        <v>2.652370929718018</v>
       </c>
     </row>
     <row r="264">
@@ -2536,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>-0.01589266210794449</v>
       </c>
     </row>
     <row r="265">
@@ -2544,7 +2544,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>0.4863885641098022</v>
       </c>
     </row>
     <row r="266">
@@ -2552,7 +2552,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>-0.09288210421800613</v>
       </c>
     </row>
     <row r="267">
@@ -2560,7 +2560,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>0.508788526058197</v>
       </c>
     </row>
     <row r="268">
@@ -2568,7 +2568,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>-0.03114493191242218</v>
       </c>
     </row>
     <row r="269">
@@ -2576,7 +2576,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>0.2162080705165863</v>
       </c>
     </row>
     <row r="270">
@@ -2584,7 +2584,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>0.2640243768692017</v>
       </c>
     </row>
     <row r="271">
@@ -2592,7 +2592,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>0.1662474870681763</v>
       </c>
     </row>
     <row r="272">
@@ -2600,7 +2600,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>-0.1521082371473312</v>
       </c>
     </row>
     <row r="273">
@@ -2608,7 +2608,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>1.098657131195068</v>
       </c>
     </row>
     <row r="274">
@@ -2616,7 +2616,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>2.199498414993286</v>
+        <v>1.523525238037109</v>
       </c>
     </row>
     <row r="275">
@@ -2624,7 +2624,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>9.144308090209961</v>
+        <v>6.308899879455566</v>
       </c>
     </row>
     <row r="276">
@@ -2632,7 +2632,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>36.80241775512695</v>
+        <v>26.12748527526855</v>
       </c>
     </row>
     <row r="277">
@@ -2640,7 +2640,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>52.61846542358398</v>
+        <v>34.01462173461914</v>
       </c>
     </row>
     <row r="278">
@@ -2648,7 +2648,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>69.46609497070312</v>
+        <v>48.50527954101562</v>
       </c>
     </row>
     <row r="279">
@@ -2656,7 +2656,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>104.4233627319336</v>
+        <v>83.53518676757812</v>
       </c>
     </row>
     <row r="280">
@@ -2664,7 +2664,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>110.5828323364258</v>
+        <v>103.7382965087891</v>
       </c>
     </row>
     <row r="281">
@@ -2672,7 +2672,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>88.99564361572266</v>
+        <v>109.08251953125</v>
       </c>
     </row>
     <row r="282">
@@ -2680,7 +2680,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>76.32456970214844</v>
+        <v>101.7825469970703</v>
       </c>
     </row>
     <row r="283">
@@ -2688,7 +2688,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>84.84055328369141</v>
+        <v>86.65955352783203</v>
       </c>
     </row>
     <row r="284">
@@ -2696,7 +2696,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>64.59085845947266</v>
+        <v>67.34935760498047</v>
       </c>
     </row>
     <row r="285">
@@ -2704,7 +2704,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>19.02132797241211</v>
+        <v>20.7028865814209</v>
       </c>
     </row>
     <row r="286">
@@ -2712,7 +2712,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>9.600499153137207</v>
+        <v>9.551264762878418</v>
       </c>
     </row>
     <row r="287">
@@ -2720,7 +2720,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>-0.9440914392471313</v>
       </c>
     </row>
     <row r="288">
@@ -2728,7 +2728,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>-0.5297315120697021</v>
       </c>
     </row>
     <row r="289">
@@ -2736,7 +2736,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>-0.6013956069946289</v>
       </c>
     </row>
     <row r="290">
@@ -2744,7 +2744,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>-0.1629573106765747</v>
       </c>
     </row>
     <row r="291">
@@ -2752,7 +2752,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>-0.05537792667746544</v>
       </c>
     </row>
     <row r="292">
@@ -2760,7 +2760,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>-0.1677105873823166</v>
       </c>
     </row>
     <row r="293">
@@ -2768,7 +2768,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>-0.08957120776176453</v>
       </c>
     </row>
     <row r="294">
@@ -2776,7 +2776,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>0.1796567142009735</v>
       </c>
     </row>
     <row r="295">
@@ -2784,7 +2784,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>0.3864321708679199</v>
       </c>
     </row>
     <row r="296">
@@ -2792,7 +2792,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>0.03938182443380356</v>
       </c>
     </row>
     <row r="297">
@@ -2800,7 +2800,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>2.633445024490356</v>
       </c>
     </row>
     <row r="298">
@@ -2808,7 +2808,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>-0.587790846824646</v>
       </c>
     </row>
     <row r="299">
@@ -2816,7 +2816,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>10.12360858917236</v>
       </c>
     </row>
     <row r="300">
@@ -2824,7 +2824,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>29.19455528259277</v>
+        <v>42.64113616943359</v>
       </c>
     </row>
     <row r="301">
@@ -2832,7 +2832,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>61.87810134887695</v>
+        <v>61.49733352661133</v>
       </c>
     </row>
     <row r="302">
@@ -2840,7 +2840,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>48.96682357788086</v>
+        <v>65.68979644775391</v>
       </c>
     </row>
     <row r="303">
@@ -2848,7 +2848,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>42.06393814086914</v>
+        <v>25.58002853393555</v>
       </c>
     </row>
     <row r="304">
@@ -2856,7 +2856,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>46.55504608154297</v>
+        <v>52.15823364257812</v>
       </c>
     </row>
     <row r="305">
@@ -2864,7 +2864,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>63.21161270141602</v>
+        <v>69.93173217773438</v>
       </c>
     </row>
     <row r="306">
@@ -2872,7 +2872,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>76.85739898681641</v>
+        <v>77.65184783935547</v>
       </c>
     </row>
     <row r="307">
@@ -2880,7 +2880,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>72.20228576660156</v>
+        <v>73.85194396972656</v>
       </c>
     </row>
     <row r="308">
@@ -2888,7 +2888,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>46.70135498046875</v>
+        <v>54.42802047729492</v>
       </c>
     </row>
     <row r="309">
@@ -2896,7 +2896,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>10.15396690368652</v>
+        <v>20.25639915466309</v>
       </c>
     </row>
     <row r="310">
@@ -2904,7 +2904,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>7.358807563781738</v>
+        <v>10.66240692138672</v>
       </c>
     </row>
     <row r="311">
@@ -2912,7 +2912,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>5.442265033721924</v>
       </c>
     </row>
     <row r="312">
@@ -2920,7 +2920,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>3.227624177932739</v>
       </c>
     </row>
     <row r="313">
@@ -2928,7 +2928,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>-7.852462291717529</v>
       </c>
     </row>
     <row r="314">
@@ -2936,7 +2936,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>-1.907154440879822</v>
       </c>
     </row>
     <row r="315">
@@ -2944,7 +2944,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>0.5850985050201416</v>
       </c>
     </row>
     <row r="316">
@@ -2952,7 +2952,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>0.6605055332183838</v>
       </c>
     </row>
     <row r="317">
@@ -2960,7 +2960,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>0.6605055332183838</v>
       </c>
     </row>
     <row r="318">
@@ -2968,7 +2968,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>0.5876830816268921</v>
       </c>
     </row>
     <row r="319">
@@ -2976,7 +2976,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>-0.186629980802536</v>
       </c>
     </row>
     <row r="320">
@@ -2984,7 +2984,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>-0.01930324360728264</v>
       </c>
     </row>
     <row r="321">
@@ -2992,7 +2992,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>0.2573041617870331</v>
       </c>
     </row>
     <row r="322">
@@ -3000,7 +3000,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>1.383988261222839</v>
       </c>
     </row>
     <row r="323">
@@ -3008,7 +3008,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>6.464619636535645</v>
+        <v>12.08686828613281</v>
       </c>
     </row>
     <row r="324">
@@ -3016,7 +3016,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>32.34829711914062</v>
+        <v>29.42163276672363</v>
       </c>
     </row>
     <row r="325">
@@ -3024,7 +3024,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>70.94345092773438</v>
+        <v>62.73917007446289</v>
       </c>
     </row>
     <row r="326">
@@ -3032,7 +3032,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>105.0053176879883</v>
+        <v>78.31452941894531</v>
       </c>
     </row>
     <row r="327">
@@ -3040,7 +3040,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>135.1609649658203</v>
+        <v>96.05288696289062</v>
       </c>
     </row>
     <row r="328">
@@ -3048,7 +3048,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>145.8953247070312</v>
+        <v>95.39794158935547</v>
       </c>
     </row>
     <row r="329">
@@ -3056,7 +3056,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>128.7709503173828</v>
+        <v>102.4429244995117</v>
       </c>
     </row>
     <row r="330">
@@ -3064,7 +3064,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>110.0009765625</v>
+        <v>99.55916595458984</v>
       </c>
     </row>
     <row r="331">
@@ -3072,7 +3072,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>99.46874237060547</v>
+        <v>74.86973571777344</v>
       </c>
     </row>
     <row r="332">
@@ -3080,7 +3080,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>67.35897064208984</v>
+        <v>57.88117980957031</v>
       </c>
     </row>
     <row r="333">
@@ -3088,7 +3088,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>17.21743202209473</v>
+        <v>19.69889259338379</v>
       </c>
     </row>
     <row r="334">
@@ -3096,7 +3096,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>8.135299682617188</v>
+        <v>14.52376747131348</v>
       </c>
     </row>
     <row r="335">
@@ -3104,7 +3104,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>6.873013019561768</v>
       </c>
     </row>
     <row r="336">
@@ -3112,7 +3112,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>3.925383567810059</v>
+        <v>4.591598510742188</v>
       </c>
     </row>
     <row r="337">
@@ -3120,7 +3120,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>2.381763935089111</v>
+        <v>4.008664608001709</v>
       </c>
     </row>
     <row r="338">
@@ -3128,7 +3128,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>0</v>
+        <v>2.270847082138062</v>
       </c>
     </row>
     <row r="339">
@@ -3136,7 +3136,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>0</v>
+        <v>-0.1857011616230011</v>
       </c>
     </row>
     <row r="340">
@@ -3144,7 +3144,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>0</v>
+        <v>-0.1437839269638062</v>
       </c>
     </row>
     <row r="341">
@@ -3152,7 +3152,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>-0.1894656717777252</v>
       </c>
     </row>
     <row r="342">
@@ -3160,7 +3160,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>0.3175495564937592</v>
       </c>
     </row>
     <row r="343">
@@ -3168,7 +3168,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>0</v>
+        <v>0.4861411154270172</v>
       </c>
     </row>
     <row r="344">
@@ -3176,7 +3176,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>0.2993369400501251</v>
       </c>
     </row>
     <row r="345">
@@ -3184,7 +3184,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>3.221279144287109</v>
       </c>
     </row>
     <row r="346">
@@ -3192,7 +3192,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>3.892472505569458</v>
+        <v>1.626293540000916</v>
       </c>
     </row>
     <row r="347">
@@ -3200,7 +3200,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>12.87892055511475</v>
+        <v>10.50520133972168</v>
       </c>
     </row>
     <row r="348">
@@ -3208,7 +3208,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>50.89651489257812</v>
+        <v>29.67975234985352</v>
       </c>
     </row>
     <row r="349">
@@ -3216,7 +3216,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>85.55739593505859</v>
+        <v>55.39793014526367</v>
       </c>
     </row>
     <row r="350">
@@ -3224,7 +3224,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>115.7553405761719</v>
+        <v>60.72327041625977</v>
       </c>
     </row>
     <row r="351">
@@ -3232,7 +3232,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>101.4729843139648</v>
+        <v>86.56666564941406</v>
       </c>
     </row>
     <row r="352">
@@ -3240,7 +3240,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>96.14981842041016</v>
+        <v>101.7860946655273</v>
       </c>
     </row>
     <row r="353">
@@ -3248,7 +3248,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>99.72265625</v>
+        <v>86.66312408447266</v>
       </c>
     </row>
     <row r="354">
@@ -3256,7 +3256,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>103.4774627685547</v>
+        <v>71.86593627929688</v>
       </c>
     </row>
     <row r="355">
@@ -3264,7 +3264,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>107.0470352172852</v>
+        <v>69.96367645263672</v>
       </c>
     </row>
     <row r="356">
@@ -3272,7 +3272,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>63.16997909545898</v>
+        <v>55.01625442504883</v>
       </c>
     </row>
     <row r="357">
@@ -3280,7 +3280,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>16.5101375579834</v>
+        <v>14.55457019805908</v>
       </c>
     </row>
     <row r="358">
@@ -3288,7 +3288,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>7.657763481140137</v>
+        <v>4.932287693023682</v>
       </c>
     </row>
     <row r="359">
@@ -3296,7 +3296,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>-1.254908084869385</v>
       </c>
     </row>
     <row r="360">
@@ -3304,7 +3304,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>0</v>
+        <v>-2.517916917800903</v>
       </c>
     </row>
     <row r="361">
@@ -3312,7 +3312,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>0</v>
+        <v>4.220465660095215</v>
       </c>
     </row>
     <row r="362">
@@ -3320,7 +3320,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>0</v>
+        <v>1.601434946060181</v>
       </c>
     </row>
     <row r="363">
@@ -3328,7 +3328,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>0</v>
+        <v>5.74238109588623</v>
       </c>
     </row>
     <row r="364">
@@ -3336,7 +3336,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>0</v>
+        <v>8.477267265319824</v>
       </c>
     </row>
     <row r="365">
@@ -3344,7 +3344,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>0</v>
+        <v>6.808300971984863</v>
       </c>
     </row>
     <row r="366">
@@ -3352,7 +3352,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>0</v>
+        <v>8.29909610748291</v>
       </c>
     </row>
     <row r="367">
@@ -3360,7 +3360,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>0</v>
+        <v>5.751023292541504</v>
       </c>
     </row>
     <row r="368">
@@ -3368,7 +3368,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>2.628967046737671</v>
+        <v>5.247842311859131</v>
       </c>
     </row>
     <row r="369">
@@ -3376,7 +3376,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>5.598834991455078</v>
+        <v>8.456298828125</v>
       </c>
     </row>
     <row r="370">
@@ -3384,7 +3384,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>7.2269606590271</v>
+        <v>11.75895404815674</v>
       </c>
     </row>
     <row r="371">
@@ -3392,7 +3392,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>6.598637580871582</v>
+        <v>20.32126426696777</v>
       </c>
     </row>
     <row r="372">
@@ -3400,7 +3400,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>32.08325576782227</v>
+        <v>37.26436233520508</v>
       </c>
     </row>
     <row r="373">
@@ -3408,7 +3408,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>56.5031623840332</v>
+        <v>63.35868072509766</v>
       </c>
     </row>
     <row r="374">
@@ -3416,7 +3416,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>24.90006828308105</v>
+        <v>69.97866058349609</v>
       </c>
     </row>
     <row r="375">
@@ -3424,7 +3424,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>55.6668586730957</v>
+        <v>40.65380477905273</v>
       </c>
     </row>
     <row r="376">
@@ -3432,7 +3432,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>62.49719619750977</v>
+        <v>32.97112655639648</v>
       </c>
     </row>
     <row r="377">
@@ -3440,7 +3440,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>62.56454467773438</v>
+        <v>32.65269088745117</v>
       </c>
     </row>
     <row r="378">
@@ -3448,7 +3448,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>61.44865798950195</v>
+        <v>52.03360366821289</v>
       </c>
     </row>
     <row r="379">
@@ -3456,7 +3456,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>74.40009307861328</v>
+        <v>58.81633758544922</v>
       </c>
     </row>
     <row r="380">
@@ -3464,7 +3464,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>19.26953315734863</v>
+        <v>59.05315780639648</v>
       </c>
     </row>
     <row r="381">
@@ -3472,7 +3472,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>10.08541584014893</v>
+        <v>17.0434627532959</v>
       </c>
     </row>
     <row r="382">
@@ -3480,7 +3480,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>8.129962921142578</v>
+        <v>4.931431770324707</v>
       </c>
     </row>
     <row r="383">
@@ -3488,7 +3488,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>0</v>
+        <v>5.755415916442871</v>
       </c>
     </row>
     <row r="384">
@@ -3496,7 +3496,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>0</v>
+        <v>3.255024671554565</v>
       </c>
     </row>
     <row r="385">
@@ -3504,7 +3504,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>0</v>
+        <v>3.866578340530396</v>
       </c>
     </row>
     <row r="386">
@@ -3512,7 +3512,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>0</v>
+        <v>3.561943531036377</v>
       </c>
     </row>
     <row r="387">
@@ -3520,7 +3520,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>4.241166591644287</v>
+        <v>-0.8169617056846619</v>
       </c>
     </row>
     <row r="388">
@@ -3528,7 +3528,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>0</v>
+        <v>2.731706619262695</v>
       </c>
     </row>
     <row r="389">
@@ -3536,7 +3536,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>0</v>
+        <v>0.3726989328861237</v>
       </c>
     </row>
     <row r="390">
@@ -3544,7 +3544,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>0</v>
+        <v>0.3598191440105438</v>
       </c>
     </row>
     <row r="391">
@@ -3552,7 +3552,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>0</v>
+        <v>0.3576702177524567</v>
       </c>
     </row>
     <row r="392">
@@ -3560,7 +3560,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>0</v>
+        <v>0.09614264965057373</v>
       </c>
     </row>
     <row r="393">
@@ -3568,7 +3568,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>3.660815238952637</v>
+        <v>4.503059387207031</v>
       </c>
     </row>
     <row r="394">
@@ -3576,7 +3576,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>0</v>
+        <v>3.904583930969238</v>
       </c>
     </row>
     <row r="395">
@@ -3584,7 +3584,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>3.385334014892578</v>
+        <v>10.53826522827148</v>
       </c>
     </row>
     <row r="396">
@@ -3592,7 +3592,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>29.8421745300293</v>
+        <v>37.68484497070312</v>
       </c>
     </row>
     <row r="397">
@@ -3600,7 +3600,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>59.264892578125</v>
+        <v>44.71382904052734</v>
       </c>
     </row>
     <row r="398">
@@ -3608,7 +3608,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>66.56285858154297</v>
+        <v>57.48154830932617</v>
       </c>
     </row>
     <row r="399">
@@ -3616,7 +3616,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>94.50526428222656</v>
+        <v>88.67460632324219</v>
       </c>
     </row>
     <row r="400">
@@ -3624,7 +3624,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>74.86916351318359</v>
+        <v>90.79740905761719</v>
       </c>
     </row>
     <row r="401">
@@ -3632,7 +3632,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>75.09345245361328</v>
+        <v>111.5396957397461</v>
       </c>
     </row>
     <row r="402">
@@ -3640,7 +3640,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>55.33110427856445</v>
+        <v>98.93943023681641</v>
       </c>
     </row>
     <row r="403">
@@ -3648,7 +3648,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>51.77520370483398</v>
+        <v>89.28266906738281</v>
       </c>
     </row>
     <row r="404">
@@ -3656,7 +3656,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>32.87649917602539</v>
+        <v>47.02709197998047</v>
       </c>
     </row>
     <row r="405">
@@ -3664,7 +3664,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>13.73771953582764</v>
+        <v>22.49262428283691</v>
       </c>
     </row>
     <row r="406">
@@ -3672,7 +3672,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>7.898832321166992</v>
+        <v>9.011560440063477</v>
       </c>
     </row>
     <row r="407">
@@ -3680,7 +3680,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>2.501360893249512</v>
+        <v>1.11963152885437</v>
       </c>
     </row>
     <row r="408">
@@ -3688,7 +3688,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>0</v>
+        <v>0.1021505445241928</v>
       </c>
     </row>
     <row r="409">
@@ -3696,7 +3696,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>-0.109952874481678</v>
       </c>
     </row>
     <row r="410">
@@ -3704,7 +3704,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>0</v>
+        <v>-0.3815471231937408</v>
       </c>
     </row>
     <row r="411">
@@ -3712,7 +3712,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>0.02800975367426872</v>
       </c>
     </row>
     <row r="412">
@@ -3720,7 +3720,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>0</v>
+        <v>-0.27765753865242</v>
       </c>
     </row>
     <row r="413">
@@ -3728,7 +3728,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>-0.6737924218177795</v>
       </c>
     </row>
     <row r="414">
@@ -3736,7 +3736,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>0</v>
+        <v>0.976614773273468</v>
       </c>
     </row>
     <row r="415">
@@ -3744,7 +3744,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>0</v>
+        <v>0.9903438687324524</v>
       </c>
     </row>
     <row r="416">
@@ -3752,7 +3752,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>0</v>
+        <v>-0.05528504773974419</v>
       </c>
     </row>
     <row r="417">
@@ -3760,7 +3760,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>1.520591974258423</v>
       </c>
     </row>
     <row r="418">
@@ -3768,7 +3768,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>0</v>
+        <v>1.272415399551392</v>
       </c>
     </row>
     <row r="419">
@@ -3776,7 +3776,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>3.447219133377075</v>
+        <v>4.041421890258789</v>
       </c>
     </row>
     <row r="420">
@@ -3784,7 +3784,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>36.30124664306641</v>
+        <v>28.41229438781738</v>
       </c>
     </row>
     <row r="421">
@@ -3792,7 +3792,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>77.15891265869141</v>
+        <v>70.51864624023438</v>
       </c>
     </row>
     <row r="422">
@@ -3800,7 +3800,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>109.6455612182617</v>
+        <v>93.38418579101562</v>
       </c>
     </row>
     <row r="423">
@@ -3808,7 +3808,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>117.4568405151367</v>
+        <v>107.7641143798828</v>
       </c>
     </row>
     <row r="424">
@@ -3816,7 +3816,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>146.5358734130859</v>
+        <v>129.9381256103516</v>
       </c>
     </row>
     <row r="425">
@@ -3824,7 +3824,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>116.7857818603516</v>
+        <v>128.4664611816406</v>
       </c>
     </row>
     <row r="426">
@@ -3832,7 +3832,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>105.9641494750977</v>
+        <v>121.7203750610352</v>
       </c>
     </row>
     <row r="427">
@@ -3840,7 +3840,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>89.61923980712891</v>
+        <v>92.45233917236328</v>
       </c>
     </row>
     <row r="428">
@@ -3848,7 +3848,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>66.24598693847656</v>
+        <v>77.50397491455078</v>
       </c>
     </row>
     <row r="429">
@@ -3856,7 +3856,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>16.16304588317871</v>
+        <v>23.36905288696289</v>
       </c>
     </row>
     <row r="430">
@@ -3864,7 +3864,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>5.261548042297363</v>
+        <v>13.47177410125732</v>
       </c>
     </row>
     <row r="431">
@@ -3872,7 +3872,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>2.094945907592773</v>
+        <v>0.2701790034770966</v>
       </c>
     </row>
     <row r="432">
@@ -3880,7 +3880,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>0</v>
+        <v>-0.1648067533969879</v>
       </c>
     </row>
     <row r="433">
@@ -3888,7 +3888,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>0</v>
+        <v>-0.09422988444566727</v>
       </c>
     </row>
     <row r="434">
@@ -3896,7 +3896,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>0</v>
+        <v>-0.2132613360881805</v>
       </c>
     </row>
     <row r="435">
@@ -3904,7 +3904,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>0</v>
+        <v>-0.358800858259201</v>
       </c>
     </row>
     <row r="436">
@@ -3912,7 +3912,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>0</v>
+        <v>-0.270886093378067</v>
       </c>
     </row>
     <row r="437">
@@ -3920,7 +3920,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>0</v>
+        <v>0.5239822864532471</v>
       </c>
     </row>
     <row r="438">
@@ -3928,7 +3928,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>0</v>
+        <v>0.6982800364494324</v>
       </c>
     </row>
     <row r="439">
@@ -3936,7 +3936,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>0</v>
+        <v>-0.03800683841109276</v>
       </c>
     </row>
     <row r="440">
@@ -3944,7 +3944,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>0</v>
+        <v>-0.3572401106357574</v>
       </c>
     </row>
     <row r="441">
@@ -3952,7 +3952,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>0</v>
+        <v>1.182864308357239</v>
       </c>
     </row>
     <row r="442">
@@ -3960,7 +3960,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>0</v>
+        <v>1.656357765197754</v>
       </c>
     </row>
     <row r="443">
@@ -3968,7 +3968,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>0</v>
+        <v>0.6631703972816467</v>
       </c>
     </row>
     <row r="444">
@@ -3976,7 +3976,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>23.82024574279785</v>
+        <v>14.49239730834961</v>
       </c>
     </row>
     <row r="445">
@@ -3984,7 +3984,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>33.54867553710938</v>
+        <v>30.85819244384766</v>
       </c>
     </row>
     <row r="446">
@@ -3992,7 +3992,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>61.98015975952148</v>
+        <v>44.64981460571289</v>
       </c>
     </row>
     <row r="447">
@@ -4000,7 +4000,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>85.911865234375</v>
+        <v>47.02526473999023</v>
       </c>
     </row>
     <row r="448">
@@ -4008,7 +4008,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>50.28585052490234</v>
+        <v>50.49227905273438</v>
       </c>
     </row>
     <row r="449">
@@ -4016,7 +4016,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>55.66136169433594</v>
+        <v>44.36748123168945</v>
       </c>
     </row>
     <row r="450">
@@ -4024,7 +4024,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>55.07158660888672</v>
+        <v>39.47186660766602</v>
       </c>
     </row>
     <row r="451">
@@ -4032,7 +4032,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>37.57307052612305</v>
+        <v>35.89836502075195</v>
       </c>
     </row>
     <row r="452">
@@ -4040,7 +4040,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>37.05068206787109</v>
+        <v>24.03483581542969</v>
       </c>
     </row>
     <row r="453">
@@ -4048,7 +4048,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>0</v>
+        <v>9.321696281433105</v>
       </c>
     </row>
     <row r="454">
@@ -4056,7 +4056,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>0</v>
+        <v>-1.081631422042847</v>
       </c>
     </row>
     <row r="455">
@@ -4064,7 +4064,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>0</v>
+        <v>-3.161941051483154</v>
       </c>
     </row>
     <row r="456">
@@ -4072,7 +4072,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>0</v>
+        <v>-3.64582633972168</v>
       </c>
     </row>
     <row r="457">
@@ -4080,7 +4080,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>0</v>
+        <v>-3.207129716873169</v>
       </c>
     </row>
     <row r="458">
@@ -4088,7 +4088,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>0</v>
+        <v>-1.714147686958313</v>
       </c>
     </row>
     <row r="459">
@@ -4096,7 +4096,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>0</v>
+        <v>-0.7319450974464417</v>
       </c>
     </row>
     <row r="460">
@@ -4104,7 +4104,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>0</v>
+        <v>-0.6033652424812317</v>
       </c>
     </row>
     <row r="461">
@@ -4112,7 +4112,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>0</v>
+        <v>-0.4307573437690735</v>
       </c>
     </row>
     <row r="462">
@@ -4120,7 +4120,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>0</v>
+        <v>-0.3939785361289978</v>
       </c>
     </row>
     <row r="463">
@@ -4128,7 +4128,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>0</v>
+        <v>-0.2545937597751617</v>
       </c>
     </row>
     <row r="464">
@@ -4136,7 +4136,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>0</v>
+        <v>-0.2689756155014038</v>
       </c>
     </row>
     <row r="465">
@@ -4144,7 +4144,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>0</v>
+        <v>1.193404674530029</v>
       </c>
     </row>
     <row r="466">
@@ -4152,7 +4152,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>0</v>
+        <v>-1.783471345901489</v>
       </c>
     </row>
     <row r="467">
@@ -4160,7 +4160,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>3.879038572311401</v>
+        <v>0.1197851821780205</v>
       </c>
     </row>
     <row r="468">
@@ -4168,7 +4168,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>26.93829345703125</v>
+        <v>12.72713279724121</v>
       </c>
     </row>
     <row r="469">
@@ -4176,7 +4176,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>26.71138763427734</v>
+        <v>35.37408447265625</v>
       </c>
     </row>
     <row r="470">
@@ -4184,7 +4184,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>47.18310165405273</v>
+        <v>38.51757049560547</v>
       </c>
     </row>
     <row r="471">
@@ -4192,7 +4192,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>90.18460083007812</v>
+        <v>19.99748039245605</v>
       </c>
     </row>
     <row r="472">
@@ -4200,7 +4200,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>96.63022613525391</v>
+        <v>82.10404968261719</v>
       </c>
     </row>
     <row r="473">
@@ -4208,7 +4208,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>83.39032745361328</v>
+        <v>61.51404571533203</v>
       </c>
     </row>
     <row r="474">
@@ -4216,7 +4216,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>52.11262130737305</v>
+        <v>52.90435791015625</v>
       </c>
     </row>
     <row r="475">
@@ -4224,7 +4224,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>53.57951354980469</v>
+        <v>36.32991409301758</v>
       </c>
     </row>
     <row r="476">
@@ -4232,7 +4232,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>59.86994934082031</v>
+        <v>30.89672088623047</v>
       </c>
     </row>
     <row r="477">
@@ -4240,7 +4240,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>12.34463596343994</v>
+        <v>17.74428749084473</v>
       </c>
     </row>
     <row r="478">
@@ -4248,7 +4248,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>6.628678321838379</v>
+        <v>5.418436050415039</v>
       </c>
     </row>
     <row r="479">
@@ -4256,7 +4256,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>0</v>
+        <v>1.237895131111145</v>
       </c>
     </row>
     <row r="480">
@@ -4264,7 +4264,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>0</v>
+        <v>-0.2061106562614441</v>
       </c>
     </row>
     <row r="481">
@@ -4272,7 +4272,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>0</v>
+        <v>0.4696092009544373</v>
       </c>
     </row>
     <row r="482">
@@ -4280,7 +4280,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="n">
-        <v>0</v>
+        <v>0.3273627460002899</v>
       </c>
     </row>
     <row r="483">
@@ -4288,7 +4288,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="n">
-        <v>0</v>
+        <v>-0.2041324973106384</v>
       </c>
     </row>
     <row r="484">
@@ -4296,7 +4296,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="n">
-        <v>0</v>
+        <v>-0.2141967117786407</v>
       </c>
     </row>
     <row r="485">
@@ -4304,7 +4304,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="n">
-        <v>0</v>
+        <v>-0.937683641910553</v>
       </c>
     </row>
     <row r="486">
@@ -4312,7 +4312,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="n">
-        <v>0</v>
+        <v>-0.7514702081680298</v>
       </c>
     </row>
     <row r="487">
@@ -4320,7 +4320,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="n">
-        <v>0</v>
+        <v>1.001086711883545</v>
       </c>
     </row>
     <row r="488">
@@ -4328,7 +4328,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="n">
-        <v>0</v>
+        <v>-0.1717982590198517</v>
       </c>
     </row>
     <row r="489">
@@ -4336,7 +4336,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="n">
-        <v>0</v>
+        <v>1.050824403762817</v>
       </c>
     </row>
     <row r="490">
@@ -4344,7 +4344,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="n">
-        <v>0</v>
+        <v>0.6764345765113831</v>
       </c>
     </row>
     <row r="491">
@@ -4352,7 +4352,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="n">
-        <v>3.366062879562378</v>
+        <v>-0.7087548971176147</v>
       </c>
     </row>
     <row r="492">
@@ -4360,7 +4360,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="n">
-        <v>20.15554618835449</v>
+        <v>8.031059265136719</v>
       </c>
     </row>
     <row r="493">
@@ -4368,7 +4368,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="n">
-        <v>42.91893768310547</v>
+        <v>34.76393508911133</v>
       </c>
     </row>
     <row r="494">
@@ -4376,7 +4376,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="n">
-        <v>43.54660034179688</v>
+        <v>28.57926940917969</v>
       </c>
     </row>
     <row r="495">
@@ -4384,7 +4384,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="n">
-        <v>39.43316268920898</v>
+        <v>30.43495178222656</v>
       </c>
     </row>
     <row r="496">
@@ -4392,7 +4392,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="n">
-        <v>26.64479064941406</v>
+        <v>36.31044769287109</v>
       </c>
     </row>
     <row r="497">
@@ -4400,7 +4400,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="n">
-        <v>34.64328002929688</v>
+        <v>31.53122901916504</v>
       </c>
     </row>
     <row r="498">
@@ -4408,7 +4408,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="n">
-        <v>29.4181079864502</v>
+        <v>41.06999969482422</v>
       </c>
     </row>
     <row r="499">
@@ -4416,7 +4416,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="n">
-        <v>31.42682647705078</v>
+        <v>27.0401668548584</v>
       </c>
     </row>
     <row r="500">
@@ -4424,7 +4424,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="n">
-        <v>53.38968276977539</v>
+        <v>34.18437957763672</v>
       </c>
     </row>
     <row r="501">
@@ -4432,7 +4432,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="n">
-        <v>10.47465133666992</v>
+        <v>18.30988502502441</v>
       </c>
     </row>
     <row r="502">
@@ -4440,7 +4440,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="n">
-        <v>0</v>
+        <v>1.003784894943237</v>
       </c>
     </row>
     <row r="503">
@@ -4448,7 +4448,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="n">
-        <v>0</v>
+        <v>-0.256709486246109</v>
       </c>
     </row>
     <row r="504">
@@ -4456,7 +4456,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="n">
-        <v>0</v>
+        <v>0.06025483831763268</v>
       </c>
     </row>
     <row r="505">
@@ -4464,7 +4464,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="n">
-        <v>0</v>
+        <v>-0.2755257785320282</v>
       </c>
     </row>
     <row r="506">
@@ -4472,7 +4472,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="n">
-        <v>0</v>
+        <v>0.07408709079027176</v>
       </c>
     </row>
     <row r="507">
@@ -4480,7 +4480,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="n">
-        <v>0</v>
+        <v>-0.4847088754177094</v>
       </c>
     </row>
     <row r="508">
@@ -4488,7 +4488,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="n">
-        <v>0</v>
+        <v>0.05816356465220451</v>
       </c>
     </row>
     <row r="509">
@@ -4496,7 +4496,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="n">
-        <v>0</v>
+        <v>-0.1854691654443741</v>
       </c>
     </row>
     <row r="510">
@@ -4504,7 +4504,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="n">
-        <v>0</v>
+        <v>-0.1097771823406219</v>
       </c>
     </row>
     <row r="511">
@@ -4512,7 +4512,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="n">
-        <v>0</v>
+        <v>0.3454701006412506</v>
       </c>
     </row>
     <row r="512">
@@ -4520,7 +4520,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="n">
-        <v>0</v>
+        <v>0.4636562764644623</v>
       </c>
     </row>
     <row r="513">
@@ -4528,7 +4528,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="n">
-        <v>0</v>
+        <v>2.145915031433105</v>
       </c>
     </row>
     <row r="514">
@@ -4536,7 +4536,7 @@
         <v>512</v>
       </c>
       <c r="B514" t="n">
-        <v>0</v>
+        <v>-0.1854457557201385</v>
       </c>
     </row>
     <row r="515">
@@ -4544,7 +4544,7 @@
         <v>513</v>
       </c>
       <c r="B515" t="n">
-        <v>3.333113670349121</v>
+        <v>8.046241760253906</v>
       </c>
     </row>
     <row r="516">
@@ -4552,7 +4552,7 @@
         <v>514</v>
       </c>
       <c r="B516" t="n">
-        <v>31.73556900024414</v>
+        <v>32.40277481079102</v>
       </c>
     </row>
     <row r="517">
@@ -4560,7 +4560,7 @@
         <v>515</v>
       </c>
       <c r="B517" t="n">
-        <v>53.77828979492188</v>
+        <v>67.22987365722656</v>
       </c>
     </row>
     <row r="518">
@@ -4568,7 +4568,7 @@
         <v>516</v>
       </c>
       <c r="B518" t="n">
-        <v>85.53023529052734</v>
+        <v>61.4786376953125</v>
       </c>
     </row>
     <row r="519">
@@ -4576,7 +4576,7 @@
         <v>517</v>
       </c>
       <c r="B519" t="n">
-        <v>108.2749633789062</v>
+        <v>100.377685546875</v>
       </c>
     </row>
     <row r="520">
@@ -4584,7 +4584,7 @@
         <v>518</v>
       </c>
       <c r="B520" t="n">
-        <v>84.07809448242188</v>
+        <v>110.130485534668</v>
       </c>
     </row>
     <row r="521">
@@ -4592,7 +4592,7 @@
         <v>519</v>
       </c>
       <c r="B521" t="n">
-        <v>61.82308959960938</v>
+        <v>100.5737457275391</v>
       </c>
     </row>
     <row r="522">
@@ -4600,7 +4600,7 @@
         <v>520</v>
       </c>
       <c r="B522" t="n">
-        <v>65.79929351806641</v>
+        <v>79.59797668457031</v>
       </c>
     </row>
     <row r="523">
@@ -4608,7 +4608,7 @@
         <v>521</v>
       </c>
       <c r="B523" t="n">
-        <v>40.07719421386719</v>
+        <v>64.6876220703125</v>
       </c>
     </row>
     <row r="524">
@@ -4616,7 +4616,7 @@
         <v>522</v>
       </c>
       <c r="B524" t="n">
-        <v>37.32764434814453</v>
+        <v>71.60084533691406</v>
       </c>
     </row>
     <row r="525">
@@ -4624,7 +4624,7 @@
         <v>523</v>
       </c>
       <c r="B525" t="n">
-        <v>9.035425186157227</v>
+        <v>15.97572040557861</v>
       </c>
     </row>
     <row r="526">
@@ -4632,7 +4632,7 @@
         <v>524</v>
       </c>
       <c r="B526" t="n">
-        <v>3.928709983825684</v>
+        <v>6.642772197723389</v>
       </c>
     </row>
     <row r="527">
@@ -4640,7 +4640,7 @@
         <v>525</v>
       </c>
       <c r="B527" t="n">
-        <v>0</v>
+        <v>1.885731101036072</v>
       </c>
     </row>
     <row r="528">
@@ -4648,7 +4648,7 @@
         <v>526</v>
       </c>
       <c r="B528" t="n">
-        <v>0</v>
+        <v>0.816178023815155</v>
       </c>
     </row>
     <row r="529">
@@ -4656,7 +4656,7 @@
         <v>527</v>
       </c>
       <c r="B529" t="n">
-        <v>0</v>
+        <v>1.453245282173157</v>
       </c>
     </row>
     <row r="530">
@@ -4664,7 +4664,7 @@
         <v>528</v>
       </c>
       <c r="B530" t="n">
-        <v>0</v>
+        <v>1.096988439559937</v>
       </c>
     </row>
     <row r="531">
@@ -4672,7 +4672,7 @@
         <v>529</v>
       </c>
       <c r="B531" t="n">
-        <v>0</v>
+        <v>0.3040289580821991</v>
       </c>
     </row>
     <row r="532">
@@ -4680,7 +4680,7 @@
         <v>530</v>
       </c>
       <c r="B532" t="n">
-        <v>0</v>
+        <v>0.2600269615650177</v>
       </c>
     </row>
     <row r="533">
@@ -4688,7 +4688,7 @@
         <v>531</v>
       </c>
       <c r="B533" t="n">
-        <v>0</v>
+        <v>0.3378891050815582</v>
       </c>
     </row>
     <row r="534">
@@ -4696,7 +4696,7 @@
         <v>532</v>
       </c>
       <c r="B534" t="n">
-        <v>0</v>
+        <v>0.2268563956022263</v>
       </c>
     </row>
     <row r="535">
@@ -4704,7 +4704,7 @@
         <v>533</v>
       </c>
       <c r="B535" t="n">
-        <v>0</v>
+        <v>0.08817514777183533</v>
       </c>
     </row>
     <row r="536">
@@ -4712,7 +4712,7 @@
         <v>534</v>
       </c>
       <c r="B536" t="n">
-        <v>0</v>
+        <v>0.05844345316290855</v>
       </c>
     </row>
     <row r="537">
@@ -4720,7 +4720,7 @@
         <v>535</v>
       </c>
       <c r="B537" t="n">
-        <v>0</v>
+        <v>2.599562883377075</v>
       </c>
     </row>
     <row r="538">
@@ -4728,7 +4728,7 @@
         <v>536</v>
       </c>
       <c r="B538" t="n">
-        <v>0</v>
+        <v>0.7871688604354858</v>
       </c>
     </row>
     <row r="539">
@@ -4736,7 +4736,7 @@
         <v>537</v>
       </c>
       <c r="B539" t="n">
-        <v>11.07494926452637</v>
+        <v>7.115793704986572</v>
       </c>
     </row>
     <row r="540">
@@ -4744,7 +4744,7 @@
         <v>538</v>
       </c>
       <c r="B540" t="n">
-        <v>44.46188354492188</v>
+        <v>33.05265808105469</v>
       </c>
     </row>
     <row r="541">
@@ -4752,7 +4752,7 @@
         <v>539</v>
       </c>
       <c r="B541" t="n">
-        <v>57.00954818725586</v>
+        <v>57.53170776367188</v>
       </c>
     </row>
     <row r="542">
@@ -4760,7 +4760,7 @@
         <v>540</v>
       </c>
       <c r="B542" t="n">
-        <v>94.80995178222656</v>
+        <v>79.27915191650391</v>
       </c>
     </row>
     <row r="543">
@@ -4768,7 +4768,7 @@
         <v>541</v>
       </c>
       <c r="B543" t="n">
-        <v>136.8587036132812</v>
+        <v>105.1792068481445</v>
       </c>
     </row>
     <row r="544">
@@ -4776,7 +4776,7 @@
         <v>542</v>
       </c>
       <c r="B544" t="n">
-        <v>131.9148712158203</v>
+        <v>109.4009780883789</v>
       </c>
     </row>
     <row r="545">
@@ -4784,7 +4784,7 @@
         <v>543</v>
       </c>
       <c r="B545" t="n">
-        <v>119.2414398193359</v>
+        <v>92.32859802246094</v>
       </c>
     </row>
     <row r="546">
@@ -4792,7 +4792,7 @@
         <v>544</v>
       </c>
       <c r="B546" t="n">
-        <v>106.703987121582</v>
+        <v>79.09214782714844</v>
       </c>
     </row>
     <row r="547">
@@ -4800,7 +4800,7 @@
         <v>545</v>
       </c>
       <c r="B547" t="n">
-        <v>103.452507019043</v>
+        <v>67.33081817626953</v>
       </c>
     </row>
     <row r="548">
@@ -4808,7 +4808,7 @@
         <v>546</v>
       </c>
       <c r="B548" t="n">
-        <v>76.49055480957031</v>
+        <v>71.8577880859375</v>
       </c>
     </row>
     <row r="549">
@@ -4816,7 +4816,7 @@
         <v>547</v>
       </c>
       <c r="B549" t="n">
-        <v>17.50974082946777</v>
+        <v>15.82480049133301</v>
       </c>
     </row>
     <row r="550">
@@ -4824,7 +4824,7 @@
         <v>548</v>
       </c>
       <c r="B550" t="n">
-        <v>7.595736503601074</v>
+        <v>7.889475345611572</v>
       </c>
     </row>
     <row r="551">
@@ -4832,7 +4832,7 @@
         <v>549</v>
       </c>
       <c r="B551" t="n">
-        <v>0</v>
+        <v>2.721529722213745</v>
       </c>
     </row>
     <row r="552">
@@ -4840,7 +4840,7 @@
         <v>550</v>
       </c>
       <c r="B552" t="n">
-        <v>0</v>
+        <v>0.7696475386619568</v>
       </c>
     </row>
     <row r="553">
@@ -4848,7 +4848,7 @@
         <v>551</v>
       </c>
       <c r="B553" t="n">
-        <v>0</v>
+        <v>0.03508633375167847</v>
       </c>
     </row>
     <row r="554">
@@ -4856,7 +4856,7 @@
         <v>552</v>
       </c>
       <c r="B554" t="n">
-        <v>0</v>
+        <v>0.4939517676830292</v>
       </c>
     </row>
     <row r="555">
@@ -4864,7 +4864,7 @@
         <v>553</v>
       </c>
       <c r="B555" t="n">
-        <v>0</v>
+        <v>0.5188050270080566</v>
       </c>
     </row>
     <row r="556">
@@ -4872,7 +4872,7 @@
         <v>554</v>
       </c>
       <c r="B556" t="n">
-        <v>0</v>
+        <v>0.2620969116687775</v>
       </c>
     </row>
     <row r="557">
@@ -4880,7 +4880,7 @@
         <v>555</v>
       </c>
       <c r="B557" t="n">
-        <v>0</v>
+        <v>0.2756727039813995</v>
       </c>
     </row>
     <row r="558">
@@ -4888,7 +4888,7 @@
         <v>556</v>
       </c>
       <c r="B558" t="n">
-        <v>0</v>
+        <v>0.2607638537883759</v>
       </c>
     </row>
     <row r="559">
@@ -4896,7 +4896,7 @@
         <v>557</v>
       </c>
       <c r="B559" t="n">
-        <v>0</v>
+        <v>1.731417059898376</v>
       </c>
     </row>
     <row r="560">
@@ -4904,7 +4904,7 @@
         <v>558</v>
       </c>
       <c r="B560" t="n">
-        <v>0</v>
+        <v>0.06053392216563225</v>
       </c>
     </row>
     <row r="561">
@@ -4912,7 +4912,7 @@
         <v>559</v>
       </c>
       <c r="B561" t="n">
-        <v>0</v>
+        <v>5.740713119506836</v>
       </c>
     </row>
     <row r="562">
@@ -4920,7 +4920,7 @@
         <v>560</v>
       </c>
       <c r="B562" t="n">
-        <v>0</v>
+        <v>-0.7585165500640869</v>
       </c>
     </row>
     <row r="563">
@@ -4928,7 +4928,7 @@
         <v>561</v>
       </c>
       <c r="B563" t="n">
-        <v>13.12051773071289</v>
+        <v>5.34376335144043</v>
       </c>
     </row>
     <row r="564">
@@ -4936,7 +4936,7 @@
         <v>562</v>
       </c>
       <c r="B564" t="n">
-        <v>33.76120376586914</v>
+        <v>30.3296070098877</v>
       </c>
     </row>
     <row r="565">
@@ -4944,7 +4944,7 @@
         <v>563</v>
       </c>
       <c r="B565" t="n">
-        <v>34.32130432128906</v>
+        <v>44.58092498779297</v>
       </c>
     </row>
     <row r="566">
@@ -4952,7 +4952,7 @@
         <v>564</v>
       </c>
       <c r="B566" t="n">
-        <v>60.42916488647461</v>
+        <v>51.49723052978516</v>
       </c>
     </row>
     <row r="567">
@@ -4960,7 +4960,7 @@
         <v>565</v>
       </c>
       <c r="B567" t="n">
-        <v>87.36991882324219</v>
+        <v>98.18247985839844</v>
       </c>
     </row>
     <row r="568">
@@ -4968,7 +4968,7 @@
         <v>566</v>
       </c>
       <c r="B568" t="n">
-        <v>58.19107437133789</v>
+        <v>108.8637619018555</v>
       </c>
     </row>
     <row r="569">
@@ -4976,7 +4976,7 @@
         <v>567</v>
       </c>
       <c r="B569" t="n">
-        <v>49.43450927734375</v>
+        <v>92.21030426025391</v>
       </c>
     </row>
     <row r="570">
@@ -4984,7 +4984,7 @@
         <v>568</v>
       </c>
       <c r="B570" t="n">
-        <v>78.26826477050781</v>
+        <v>73.59341430664062</v>
       </c>
     </row>
     <row r="571">
@@ -4992,7 +4992,7 @@
         <v>569</v>
       </c>
       <c r="B571" t="n">
-        <v>39.09975051879883</v>
+        <v>67.91831207275391</v>
       </c>
     </row>
     <row r="572">
@@ -5000,7 +5000,7 @@
         <v>570</v>
       </c>
       <c r="B572" t="n">
-        <v>28.0393238067627</v>
+        <v>40.9254264831543</v>
       </c>
     </row>
     <row r="573">
@@ -5008,7 +5008,7 @@
         <v>571</v>
       </c>
       <c r="B573" t="n">
-        <v>10.33291816711426</v>
+        <v>9.569228172302246</v>
       </c>
     </row>
     <row r="574">
@@ -5016,7 +5016,7 @@
         <v>572</v>
       </c>
       <c r="B574" t="n">
-        <v>4.127227783203125</v>
+        <v>3.652005910873413</v>
       </c>
     </row>
     <row r="575">
@@ -5024,7 +5024,7 @@
         <v>573</v>
       </c>
       <c r="B575" t="n">
-        <v>0</v>
+        <v>1.105494737625122</v>
       </c>
     </row>
     <row r="576">
@@ -5032,7 +5032,7 @@
         <v>574</v>
       </c>
       <c r="B576" t="n">
-        <v>0</v>
+        <v>1.95766806602478</v>
       </c>
     </row>
     <row r="577">
@@ -5040,7 +5040,7 @@
         <v>575</v>
       </c>
       <c r="B577" t="n">
-        <v>0</v>
+        <v>-1.189286351203918</v>
       </c>
     </row>
     <row r="578">
@@ -5048,7 +5048,7 @@
         <v>576</v>
       </c>
       <c r="B578" t="n">
-        <v>0</v>
+        <v>0.599334716796875</v>
       </c>
     </row>
     <row r="579">
@@ -5056,7 +5056,7 @@
         <v>577</v>
       </c>
       <c r="B579" t="n">
-        <v>0</v>
+        <v>-0.5331190824508667</v>
       </c>
     </row>
     <row r="580">
@@ -5064,7 +5064,7 @@
         <v>578</v>
       </c>
       <c r="B580" t="n">
-        <v>0</v>
+        <v>0.03500563651323318</v>
       </c>
     </row>
     <row r="581">
@@ -5072,7 +5072,7 @@
         <v>579</v>
       </c>
       <c r="B581" t="n">
-        <v>0</v>
+        <v>-0.209681436419487</v>
       </c>
     </row>
     <row r="582">
@@ -5080,7 +5080,7 @@
         <v>580</v>
       </c>
       <c r="B582" t="n">
-        <v>0</v>
+        <v>0.3465352058410645</v>
       </c>
     </row>
     <row r="583">
@@ -5088,7 +5088,7 @@
         <v>581</v>
       </c>
       <c r="B583" t="n">
-        <v>0</v>
+        <v>0.4409814476966858</v>
       </c>
     </row>
     <row r="584">
@@ -5096,7 +5096,7 @@
         <v>582</v>
       </c>
       <c r="B584" t="n">
-        <v>0</v>
+        <v>0.7472721338272095</v>
       </c>
     </row>
     <row r="585">
@@ -5104,7 +5104,7 @@
         <v>583</v>
       </c>
       <c r="B585" t="n">
-        <v>0</v>
+        <v>2.471401929855347</v>
       </c>
     </row>
     <row r="586">
@@ -5112,7 +5112,7 @@
         <v>584</v>
       </c>
       <c r="B586" t="n">
-        <v>0</v>
+        <v>0.8813437223434448</v>
       </c>
     </row>
     <row r="587">
@@ -5120,7 +5120,7 @@
         <v>585</v>
       </c>
       <c r="B587" t="n">
-        <v>0</v>
+        <v>3.910340547561646</v>
       </c>
     </row>
     <row r="588">
@@ -5128,7 +5128,7 @@
         <v>586</v>
       </c>
       <c r="B588" t="n">
-        <v>2.673653364181519</v>
+        <v>10.91006946563721</v>
       </c>
     </row>
     <row r="589">
@@ -5136,7 +5136,7 @@
         <v>587</v>
       </c>
       <c r="B589" t="n">
-        <v>19.01944351196289</v>
+        <v>10.6094274520874</v>
       </c>
     </row>
     <row r="590">
@@ -5144,7 +5144,7 @@
         <v>588</v>
       </c>
       <c r="B590" t="n">
-        <v>23.73932266235352</v>
+        <v>11.28182601928711</v>
       </c>
     </row>
     <row r="591">
@@ -5152,7 +5152,7 @@
         <v>589</v>
       </c>
       <c r="B591" t="n">
-        <v>29.95164108276367</v>
+        <v>21.80890274047852</v>
       </c>
     </row>
     <row r="592">
@@ -5160,7 +5160,7 @@
         <v>590</v>
       </c>
       <c r="B592" t="n">
-        <v>29.04600715637207</v>
+        <v>46.73056411743164</v>
       </c>
     </row>
     <row r="593">
@@ -5168,7 +5168,7 @@
         <v>591</v>
       </c>
       <c r="B593" t="n">
-        <v>53.4241943359375</v>
+        <v>27.17925071716309</v>
       </c>
     </row>
     <row r="594">
@@ -5176,7 +5176,7 @@
         <v>592</v>
       </c>
       <c r="B594" t="n">
-        <v>39.78718948364258</v>
+        <v>34.78357696533203</v>
       </c>
     </row>
     <row r="595">
@@ -5184,7 +5184,7 @@
         <v>593</v>
       </c>
       <c r="B595" t="n">
-        <v>36.16458511352539</v>
+        <v>34.68326950073242</v>
       </c>
     </row>
     <row r="596">
@@ -5192,7 +5192,7 @@
         <v>594</v>
       </c>
       <c r="B596" t="n">
-        <v>38.37761688232422</v>
+        <v>40.63480758666992</v>
       </c>
     </row>
     <row r="597">
@@ -5200,7 +5200,7 @@
         <v>595</v>
       </c>
       <c r="B597" t="n">
-        <v>9.788707733154297</v>
+        <v>6.857966899871826</v>
       </c>
     </row>
     <row r="598">
@@ -5208,7 +5208,7 @@
         <v>596</v>
       </c>
       <c r="B598" t="n">
-        <v>0</v>
+        <v>1.4411381483078</v>
       </c>
     </row>
     <row r="599">
@@ -5216,7 +5216,7 @@
         <v>597</v>
       </c>
       <c r="B599" t="n">
-        <v>0</v>
+        <v>-0.640174388885498</v>
       </c>
     </row>
     <row r="600">
@@ -5224,7 +5224,7 @@
         <v>598</v>
       </c>
       <c r="B600" t="n">
-        <v>0</v>
+        <v>-0.9205384254455566</v>
       </c>
     </row>
     <row r="601">
@@ -5232,7 +5232,7 @@
         <v>599</v>
       </c>
       <c r="B601" t="n">
-        <v>0</v>
+        <v>-2.083959102630615</v>
       </c>
     </row>
     <row r="602">
@@ -5240,7 +5240,7 @@
         <v>600</v>
       </c>
       <c r="B602" t="n">
-        <v>2.539744138717651</v>
+        <v>-0.5039350986480713</v>
       </c>
     </row>
     <row r="603">
@@ -5248,7 +5248,7 @@
         <v>601</v>
       </c>
       <c r="B603" t="n">
-        <v>13.28768920898438</v>
+        <v>-1.846565842628479</v>
       </c>
     </row>
     <row r="604">
@@ -5256,7 +5256,7 @@
         <v>602</v>
       </c>
       <c r="B604" t="n">
-        <v>5.852958679199219</v>
+        <v>3.658334493637085</v>
       </c>
     </row>
     <row r="605">
@@ -5264,7 +5264,7 @@
         <v>603</v>
       </c>
       <c r="B605" t="n">
-        <v>0</v>
+        <v>3.432328462600708</v>
       </c>
     </row>
     <row r="606">
@@ -5272,7 +5272,7 @@
         <v>604</v>
       </c>
       <c r="B606" t="n">
-        <v>0</v>
+        <v>0.5063790082931519</v>
       </c>
     </row>
     <row r="607">
@@ -5280,7 +5280,7 @@
         <v>605</v>
       </c>
       <c r="B607" t="n">
-        <v>0</v>
+        <v>1.159886837005615</v>
       </c>
     </row>
     <row r="608">
@@ -5288,7 +5288,7 @@
         <v>606</v>
       </c>
       <c r="B608" t="n">
-        <v>0</v>
+        <v>6.154837131500244</v>
       </c>
     </row>
     <row r="609">
@@ -5296,7 +5296,7 @@
         <v>607</v>
       </c>
       <c r="B609" t="n">
-        <v>12.71562957763672</v>
+        <v>8.52308464050293</v>
       </c>
     </row>
     <row r="610">
@@ -5304,7 +5304,7 @@
         <v>608</v>
       </c>
       <c r="B610" t="n">
-        <v>2.443726778030396</v>
+        <v>11.56115531921387</v>
       </c>
     </row>
     <row r="611">
@@ -5312,7 +5312,7 @@
         <v>609</v>
       </c>
       <c r="B611" t="n">
-        <v>0</v>
+        <v>20.2092227935791</v>
       </c>
     </row>
     <row r="612">
@@ -5320,7 +5320,7 @@
         <v>610</v>
       </c>
       <c r="B612" t="n">
-        <v>16.40608978271484</v>
+        <v>32.71273040771484</v>
       </c>
     </row>
     <row r="613">
@@ -5328,7 +5328,7 @@
         <v>611</v>
       </c>
       <c r="B613" t="n">
-        <v>22.6429443359375</v>
+        <v>41.86420059204102</v>
       </c>
     </row>
     <row r="614">
@@ -5336,7 +5336,7 @@
         <v>612</v>
       </c>
       <c r="B614" t="n">
-        <v>21.17756843566895</v>
+        <v>50.66007995605469</v>
       </c>
     </row>
     <row r="615">
@@ -5344,7 +5344,7 @@
         <v>613</v>
       </c>
       <c r="B615" t="n">
-        <v>35.24699020385742</v>
+        <v>37.64165115356445</v>
       </c>
     </row>
     <row r="616">
@@ -5352,7 +5352,7 @@
         <v>614</v>
       </c>
       <c r="B616" t="n">
-        <v>34.3005485534668</v>
+        <v>42.29051971435547</v>
       </c>
     </row>
     <row r="617">
@@ -5360,7 +5360,7 @@
         <v>615</v>
       </c>
       <c r="B617" t="n">
-        <v>48.42384719848633</v>
+        <v>38.06992721557617</v>
       </c>
     </row>
     <row r="618">
@@ -5368,7 +5368,7 @@
         <v>616</v>
       </c>
       <c r="B618" t="n">
-        <v>49.50646591186523</v>
+        <v>40.70851898193359</v>
       </c>
     </row>
     <row r="619">
@@ -5376,7 +5376,7 @@
         <v>617</v>
       </c>
       <c r="B619" t="n">
-        <v>48.23822402954102</v>
+        <v>45.13429260253906</v>
       </c>
     </row>
     <row r="620">
@@ -5384,7 +5384,7 @@
         <v>618</v>
       </c>
       <c r="B620" t="n">
-        <v>52.00980758666992</v>
+        <v>34.37610244750977</v>
       </c>
     </row>
     <row r="621">
@@ -5392,7 +5392,7 @@
         <v>619</v>
       </c>
       <c r="B621" t="n">
-        <v>5.296302318572998</v>
+        <v>12.7112865447998</v>
       </c>
     </row>
     <row r="622">
@@ -5400,7 +5400,7 @@
         <v>620</v>
       </c>
       <c r="B622" t="n">
-        <v>5.494591236114502</v>
+        <v>7.457034587860107</v>
       </c>
     </row>
     <row r="623">
@@ -5408,7 +5408,7 @@
         <v>621</v>
       </c>
       <c r="B623" t="n">
-        <v>0</v>
+        <v>-0.0627545565366745</v>
       </c>
     </row>
     <row r="624">
@@ -5416,7 +5416,7 @@
         <v>622</v>
       </c>
       <c r="B624" t="n">
-        <v>0</v>
+        <v>-0.5509651303291321</v>
       </c>
     </row>
     <row r="625">
@@ -5424,7 +5424,7 @@
         <v>623</v>
       </c>
       <c r="B625" t="n">
-        <v>0</v>
+        <v>1.452778935432434</v>
       </c>
     </row>
     <row r="626">
@@ -5432,7 +5432,7 @@
         <v>624</v>
       </c>
       <c r="B626" t="n">
-        <v>0</v>
+        <v>-0.7464014887809753</v>
       </c>
     </row>
     <row r="627">
@@ -5440,7 +5440,7 @@
         <v>625</v>
       </c>
       <c r="B627" t="n">
-        <v>0</v>
+        <v>1.564478278160095</v>
       </c>
     </row>
     <row r="628">
@@ -5448,7 +5448,7 @@
         <v>626</v>
       </c>
       <c r="B628" t="n">
-        <v>0</v>
+        <v>0.5049940943717957</v>
       </c>
     </row>
     <row r="629">
@@ -5456,7 +5456,7 @@
         <v>627</v>
       </c>
       <c r="B629" t="n">
-        <v>0</v>
+        <v>0.2857754528522491</v>
       </c>
     </row>
     <row r="630">
@@ -5464,7 +5464,7 @@
         <v>628</v>
       </c>
       <c r="B630" t="n">
-        <v>0</v>
+        <v>0.01342636439949274</v>
       </c>
     </row>
     <row r="631">
@@ -5472,7 +5472,7 @@
         <v>629</v>
       </c>
       <c r="B631" t="n">
-        <v>0</v>
+        <v>-1.009814620018005</v>
       </c>
     </row>
     <row r="632">
@@ -5480,7 +5480,7 @@
         <v>630</v>
       </c>
       <c r="B632" t="n">
-        <v>0</v>
+        <v>-0.615551769733429</v>
       </c>
     </row>
     <row r="633">
@@ -5488,7 +5488,7 @@
         <v>631</v>
       </c>
       <c r="B633" t="n">
-        <v>0</v>
+        <v>-1.692069888114929</v>
       </c>
     </row>
     <row r="634">
@@ -5496,7 +5496,7 @@
         <v>632</v>
       </c>
       <c r="B634" t="n">
-        <v>0</v>
+        <v>-0.01556301116943359</v>
       </c>
     </row>
     <row r="635">
@@ -5504,7 +5504,7 @@
         <v>633</v>
       </c>
       <c r="B635" t="n">
-        <v>5.76039981842041</v>
+        <v>10.29709625244141</v>
       </c>
     </row>
     <row r="636">
@@ -5512,7 +5512,7 @@
         <v>634</v>
       </c>
       <c r="B636" t="n">
-        <v>33.28133392333984</v>
+        <v>37.56895446777344</v>
       </c>
     </row>
     <row r="637">
@@ -5520,7 +5520,7 @@
         <v>635</v>
       </c>
       <c r="B637" t="n">
-        <v>67.81148529052734</v>
+        <v>72.62314605712891</v>
       </c>
     </row>
     <row r="638">
@@ -5528,7 +5528,7 @@
         <v>636</v>
       </c>
       <c r="B638" t="n">
-        <v>107.9542922973633</v>
+        <v>96.32825469970703</v>
       </c>
     </row>
     <row r="639">
@@ -5536,7 +5536,7 @@
         <v>637</v>
       </c>
       <c r="B639" t="n">
-        <v>92.57579803466797</v>
+        <v>124.551025390625</v>
       </c>
     </row>
     <row r="640">
@@ -5544,7 +5544,7 @@
         <v>638</v>
       </c>
       <c r="B640" t="n">
-        <v>127.0664291381836</v>
+        <v>120.8668975830078</v>
       </c>
     </row>
     <row r="641">
@@ -5552,7 +5552,7 @@
         <v>639</v>
       </c>
       <c r="B641" t="n">
-        <v>116.4194946289062</v>
+        <v>104.0382385253906</v>
       </c>
     </row>
     <row r="642">
@@ -5560,7 +5560,7 @@
         <v>640</v>
       </c>
       <c r="B642" t="n">
-        <v>92.90421295166016</v>
+        <v>94.15511322021484</v>
       </c>
     </row>
     <row r="643">
@@ -5568,7 +5568,7 @@
         <v>641</v>
       </c>
       <c r="B643" t="n">
-        <v>81.19622039794922</v>
+        <v>71.73015594482422</v>
       </c>
     </row>
     <row r="644">
@@ -5576,7 +5576,7 @@
         <v>642</v>
       </c>
       <c r="B644" t="n">
-        <v>53.28341674804688</v>
+        <v>51.29241180419922</v>
       </c>
     </row>
     <row r="645">
@@ -5584,7 +5584,7 @@
         <v>643</v>
       </c>
       <c r="B645" t="n">
-        <v>0</v>
+        <v>15.25524711608887</v>
       </c>
     </row>
     <row r="646">
@@ -5592,7 +5592,7 @@
         <v>644</v>
       </c>
       <c r="B646" t="n">
-        <v>0</v>
+        <v>5.440503597259521</v>
       </c>
     </row>
     <row r="647">
@@ -5600,7 +5600,7 @@
         <v>645</v>
       </c>
       <c r="B647" t="n">
-        <v>0</v>
+        <v>1.76681661605835</v>
       </c>
     </row>
     <row r="648">
@@ -5608,7 +5608,7 @@
         <v>646</v>
       </c>
       <c r="B648" t="n">
-        <v>0</v>
+        <v>3.049614667892456</v>
       </c>
     </row>
     <row r="649">
@@ -5616,7 +5616,7 @@
         <v>647</v>
       </c>
       <c r="B649" t="n">
-        <v>0</v>
+        <v>2.334991216659546</v>
       </c>
     </row>
     <row r="650">
@@ -5624,7 +5624,7 @@
         <v>648</v>
       </c>
       <c r="B650" t="n">
-        <v>2.433868646621704</v>
+        <v>2.809589385986328</v>
       </c>
     </row>
     <row r="651">
@@ -5632,7 +5632,7 @@
         <v>649</v>
       </c>
       <c r="B651" t="n">
-        <v>0</v>
+        <v>0.7498294115066528</v>
       </c>
     </row>
     <row r="652">
@@ -5640,7 +5640,7 @@
         <v>650</v>
       </c>
       <c r="B652" t="n">
-        <v>0</v>
+        <v>0.1219826489686966</v>
       </c>
     </row>
     <row r="653">
@@ -5648,7 +5648,7 @@
         <v>651</v>
       </c>
       <c r="B653" t="n">
-        <v>0</v>
+        <v>0.1916646361351013</v>
       </c>
     </row>
     <row r="654">
@@ -5656,7 +5656,7 @@
         <v>652</v>
       </c>
       <c r="B654" t="n">
-        <v>0</v>
+        <v>0.1686478853225708</v>
       </c>
     </row>
     <row r="655">
@@ -5664,7 +5664,7 @@
         <v>653</v>
       </c>
       <c r="B655" t="n">
-        <v>0</v>
+        <v>0.3864805698394775</v>
       </c>
     </row>
     <row r="656">
@@ -5672,7 +5672,7 @@
         <v>654</v>
       </c>
       <c r="B656" t="n">
-        <v>0</v>
+        <v>0.1181012094020844</v>
       </c>
     </row>
     <row r="657">
@@ -5680,7 +5680,7 @@
         <v>655</v>
       </c>
       <c r="B657" t="n">
-        <v>0</v>
+        <v>2.511834144592285</v>
       </c>
     </row>
     <row r="658">
@@ -5688,7 +5688,7 @@
         <v>656</v>
       </c>
       <c r="B658" t="n">
-        <v>9.22971248626709</v>
+        <v>2.952396869659424</v>
       </c>
     </row>
     <row r="659">
@@ -5696,7 +5696,7 @@
         <v>657</v>
       </c>
       <c r="B659" t="n">
-        <v>18.39388656616211</v>
+        <v>5.449746131896973</v>
       </c>
     </row>
     <row r="660">
@@ -5704,7 +5704,7 @@
         <v>658</v>
       </c>
       <c r="B660" t="n">
-        <v>57.09622573852539</v>
+        <v>41.45071792602539</v>
       </c>
     </row>
     <row r="661">
@@ -5712,7 +5712,7 @@
         <v>659</v>
       </c>
       <c r="B661" t="n">
-        <v>69.58022308349609</v>
+        <v>79.87252807617188</v>
       </c>
     </row>
     <row r="662">
@@ -5720,7 +5720,7 @@
         <v>660</v>
       </c>
       <c r="B662" t="n">
-        <v>90.99019622802734</v>
+        <v>78.48041534423828</v>
       </c>
     </row>
     <row r="663">
@@ -5728,7 +5728,7 @@
         <v>661</v>
       </c>
       <c r="B663" t="n">
-        <v>90.49233245849609</v>
+        <v>103.495002746582</v>
       </c>
     </row>
     <row r="664">
@@ -5736,7 +5736,7 @@
         <v>662</v>
       </c>
       <c r="B664" t="n">
-        <v>94.32182312011719</v>
+        <v>114.7180633544922</v>
       </c>
     </row>
     <row r="665">
@@ -5744,7 +5744,7 @@
         <v>663</v>
       </c>
       <c r="B665" t="n">
-        <v>87.64633178710938</v>
+        <v>96.90840911865234</v>
       </c>
     </row>
     <row r="666">
@@ -5752,7 +5752,7 @@
         <v>664</v>
       </c>
       <c r="B666" t="n">
-        <v>96.17210388183594</v>
+        <v>79.70182800292969</v>
       </c>
     </row>
     <row r="667">
@@ -5760,7 +5760,7 @@
         <v>665</v>
       </c>
       <c r="B667" t="n">
-        <v>72.66506195068359</v>
+        <v>66.62818145751953</v>
       </c>
     </row>
     <row r="668">
@@ -5768,7 +5768,7 @@
         <v>666</v>
       </c>
       <c r="B668" t="n">
-        <v>55.75096130371094</v>
+        <v>50.49635696411133</v>
       </c>
     </row>
     <row r="669">
@@ -5776,7 +5776,7 @@
         <v>667</v>
       </c>
       <c r="B669" t="n">
-        <v>10.93734073638916</v>
+        <v>8.929805755615234</v>
       </c>
     </row>
     <row r="670">
@@ -5784,7 +5784,7 @@
         <v>668</v>
       </c>
       <c r="B670" t="n">
-        <v>6.357084274291992</v>
+        <v>2.685019731521606</v>
       </c>
     </row>
     <row r="671">
@@ -5792,7 +5792,7 @@
         <v>669</v>
       </c>
       <c r="B671" t="n">
-        <v>4.017863750457764</v>
+        <v>-2.573987245559692</v>
       </c>
     </row>
     <row r="672">
@@ -5800,7 +5800,7 @@
         <v>670</v>
       </c>
       <c r="B672" t="n">
-        <v>0</v>
+        <v>-2.059995174407959</v>
       </c>
     </row>
     <row r="673">
@@ -5808,7 +5808,7 @@
         <v>671</v>
       </c>
       <c r="B673" t="n">
-        <v>2.013233661651611</v>
+        <v>1.151284694671631</v>
       </c>
     </row>
     <row r="674">
@@ -5816,7 +5816,7 @@
         <v>672</v>
       </c>
       <c r="B674" t="n">
-        <v>0</v>
+        <v>0.47964808344841</v>
       </c>
     </row>
     <row r="675">
@@ -5824,7 +5824,7 @@
         <v>673</v>
       </c>
       <c r="B675" t="n">
-        <v>0</v>
+        <v>2.068472146987915</v>
       </c>
     </row>
     <row r="676">
@@ -5832,7 +5832,7 @@
         <v>674</v>
       </c>
       <c r="B676" t="n">
-        <v>0</v>
+        <v>0.6942561864852905</v>
       </c>
     </row>
     <row r="677">
@@ -5840,7 +5840,7 @@
         <v>675</v>
       </c>
       <c r="B677" t="n">
-        <v>0</v>
+        <v>0.5440582036972046</v>
       </c>
     </row>
     <row r="678">
@@ -5848,7 +5848,7 @@
         <v>676</v>
       </c>
       <c r="B678" t="n">
-        <v>0</v>
+        <v>-0.3793587386608124</v>
       </c>
     </row>
     <row r="679">
@@ -5856,7 +5856,7 @@
         <v>677</v>
       </c>
       <c r="B679" t="n">
-        <v>0</v>
+        <v>0.652442455291748</v>
       </c>
     </row>
     <row r="680">
@@ -5864,7 +5864,7 @@
         <v>678</v>
       </c>
       <c r="B680" t="n">
-        <v>0</v>
+        <v>0.49471315741539</v>
       </c>
     </row>
     <row r="681">
@@ -5872,7 +5872,7 @@
         <v>679</v>
       </c>
       <c r="B681" t="n">
-        <v>0</v>
+        <v>2.410853624343872</v>
       </c>
     </row>
     <row r="682">
@@ -5880,7 +5880,7 @@
         <v>680</v>
       </c>
       <c r="B682" t="n">
-        <v>0</v>
+        <v>-0.1207836344838142</v>
       </c>
     </row>
     <row r="683">
@@ -5888,7 +5888,7 @@
         <v>681</v>
       </c>
       <c r="B683" t="n">
-        <v>6.658145904541016</v>
+        <v>3.02629017829895</v>
       </c>
     </row>
     <row r="684">
@@ -5896,7 +5896,7 @@
         <v>682</v>
       </c>
       <c r="B684" t="n">
-        <v>22.9433479309082</v>
+        <v>27.64307594299316</v>
       </c>
     </row>
     <row r="685">
@@ -5904,7 +5904,7 @@
         <v>683</v>
       </c>
       <c r="B685" t="n">
-        <v>43.58988189697266</v>
+        <v>52.9414176940918</v>
       </c>
     </row>
     <row r="686">
@@ -5912,7 +5912,7 @@
         <v>684</v>
       </c>
       <c r="B686" t="n">
-        <v>61.07010269165039</v>
+        <v>106.5212707519531</v>
       </c>
     </row>
     <row r="687">
@@ -5920,7 +5920,7 @@
         <v>685</v>
       </c>
       <c r="B687" t="n">
-        <v>91.12676239013672</v>
+        <v>78.68348693847656</v>
       </c>
     </row>
     <row r="688">
@@ -5928,7 +5928,7 @@
         <v>686</v>
       </c>
       <c r="B688" t="n">
-        <v>85.74718475341797</v>
+        <v>80.28250885009766</v>
       </c>
     </row>
     <row r="689">
@@ -5936,7 +5936,7 @@
         <v>687</v>
       </c>
       <c r="B689" t="n">
-        <v>89.39439392089844</v>
+        <v>81.95844268798828</v>
       </c>
     </row>
     <row r="690">
@@ -5944,7 +5944,7 @@
         <v>688</v>
       </c>
       <c r="B690" t="n">
-        <v>78.52721405029297</v>
+        <v>81.34722900390625</v>
       </c>
     </row>
     <row r="691">
@@ -5952,7 +5952,7 @@
         <v>689</v>
       </c>
       <c r="B691" t="n">
-        <v>52.5241584777832</v>
+        <v>74.70814514160156</v>
       </c>
     </row>
     <row r="692">
@@ -5960,7 +5960,7 @@
         <v>690</v>
       </c>
       <c r="B692" t="n">
-        <v>40.4958610534668</v>
+        <v>31.3978271484375</v>
       </c>
     </row>
     <row r="693">
@@ -5968,7 +5968,7 @@
         <v>691</v>
       </c>
       <c r="B693" t="n">
-        <v>8.802004814147949</v>
+        <v>14.59365749359131</v>
       </c>
     </row>
     <row r="694">
@@ -5976,7 +5976,7 @@
         <v>692</v>
       </c>
       <c r="B694" t="n">
-        <v>4.431384563446045</v>
+        <v>7.314235210418701</v>
       </c>
     </row>
     <row r="695">
@@ -5984,7 +5984,7 @@
         <v>693</v>
       </c>
       <c r="B695" t="n">
-        <v>0</v>
+        <v>1.826707482337952</v>
       </c>
     </row>
     <row r="696">
@@ -5992,7 +5992,7 @@
         <v>694</v>
       </c>
       <c r="B696" t="n">
-        <v>0</v>
+        <v>1.592910408973694</v>
       </c>
     </row>
     <row r="697">
@@ -6000,7 +6000,7 @@
         <v>695</v>
       </c>
       <c r="B697" t="n">
-        <v>0</v>
+        <v>0.859188973903656</v>
       </c>
     </row>
     <row r="698">
@@ -6008,7 +6008,7 @@
         <v>696</v>
       </c>
       <c r="B698" t="n">
-        <v>0</v>
+        <v>0.3461761176586151</v>
       </c>
     </row>
     <row r="699">
@@ -6016,7 +6016,7 @@
         <v>697</v>
       </c>
       <c r="B699" t="n">
-        <v>0</v>
+        <v>0.04416841268539429</v>
       </c>
     </row>
     <row r="700">
@@ -6024,7 +6024,7 @@
         <v>698</v>
       </c>
       <c r="B700" t="n">
-        <v>0</v>
+        <v>0.1072458624839783</v>
       </c>
     </row>
     <row r="701">
@@ -6032,7 +6032,7 @@
         <v>699</v>
       </c>
       <c r="B701" t="n">
-        <v>0</v>
+        <v>-1.532420873641968</v>
       </c>
     </row>
     <row r="702">
@@ -6040,7 +6040,7 @@
         <v>700</v>
       </c>
       <c r="B702" t="n">
-        <v>0</v>
+        <v>0.07916177064180374</v>
       </c>
     </row>
     <row r="703">
@@ -6048,7 +6048,7 @@
         <v>701</v>
       </c>
       <c r="B703" t="n">
-        <v>0</v>
+        <v>0.5010249018669128</v>
       </c>
     </row>
     <row r="704">
@@ -6056,7 +6056,7 @@
         <v>702</v>
       </c>
       <c r="B704" t="n">
-        <v>0</v>
+        <v>0.5211064219474792</v>
       </c>
     </row>
     <row r="705">
@@ -6064,7 +6064,7 @@
         <v>703</v>
       </c>
       <c r="B705" t="n">
-        <v>0</v>
+        <v>3.726667404174805</v>
       </c>
     </row>
     <row r="706">
@@ -6072,7 +6072,7 @@
         <v>704</v>
       </c>
       <c r="B706" t="n">
-        <v>0</v>
+        <v>1.087654709815979</v>
       </c>
     </row>
     <row r="707">
@@ -6080,7 +6080,7 @@
         <v>705</v>
       </c>
       <c r="B707" t="n">
-        <v>4.465717315673828</v>
+        <v>5.626903533935547</v>
       </c>
     </row>
     <row r="708">
@@ -6088,7 +6088,7 @@
         <v>706</v>
       </c>
       <c r="B708" t="n">
-        <v>18.76139831542969</v>
+        <v>29.70861434936523</v>
       </c>
     </row>
     <row r="709">
@@ -6096,7 +6096,7 @@
         <v>707</v>
       </c>
       <c r="B709" t="n">
-        <v>36.38789749145508</v>
+        <v>62.08720779418945</v>
       </c>
     </row>
     <row r="710">
@@ -6104,7 +6104,7 @@
         <v>708</v>
       </c>
       <c r="B710" t="n">
-        <v>58.52077865600586</v>
+        <v>98.30136871337891</v>
       </c>
     </row>
     <row r="711">
@@ -6112,7 +6112,7 @@
         <v>709</v>
       </c>
       <c r="B711" t="n">
-        <v>61.06560134887695</v>
+        <v>88.93938446044922</v>
       </c>
     </row>
     <row r="712">
@@ -6120,7 +6120,7 @@
         <v>710</v>
       </c>
       <c r="B712" t="n">
-        <v>84.74383544921875</v>
+        <v>87.60798645019531</v>
       </c>
     </row>
     <row r="713">
@@ -6128,7 +6128,7 @@
         <v>711</v>
       </c>
       <c r="B713" t="n">
-        <v>86.79386138916016</v>
+        <v>97.96997833251953</v>
       </c>
     </row>
     <row r="714">
@@ -6136,7 +6136,7 @@
         <v>712</v>
       </c>
       <c r="B714" t="n">
-        <v>77.06223297119141</v>
+        <v>89.39544677734375</v>
       </c>
     </row>
     <row r="715">
@@ -6144,7 +6144,7 @@
         <v>713</v>
       </c>
       <c r="B715" t="n">
-        <v>51.98389434814453</v>
+        <v>83.02520751953125</v>
       </c>
     </row>
     <row r="716">
@@ -6152,7 +6152,7 @@
         <v>714</v>
       </c>
       <c r="B716" t="n">
-        <v>35.81106567382812</v>
+        <v>39.76250457763672</v>
       </c>
     </row>
     <row r="717">
@@ -6160,7 +6160,7 @@
         <v>715</v>
       </c>
       <c r="B717" t="n">
-        <v>6.095005035400391</v>
+        <v>15.79123210906982</v>
       </c>
     </row>
     <row r="718">
@@ -6168,7 +6168,7 @@
         <v>716</v>
       </c>
       <c r="B718" t="n">
-        <v>0</v>
+        <v>7.304083347320557</v>
       </c>
     </row>
     <row r="719">
@@ -6176,7 +6176,7 @@
         <v>717</v>
       </c>
       <c r="B719" t="n">
-        <v>0</v>
+        <v>0.7108847498893738</v>
       </c>
     </row>
     <row r="720">
@@ -6184,7 +6184,7 @@
         <v>718</v>
       </c>
       <c r="B720" t="n">
-        <v>0</v>
+        <v>-0.1617129445075989</v>
       </c>
     </row>
     <row r="721">
@@ -6192,7 +6192,7 @@
         <v>719</v>
       </c>
       <c r="B721" t="n">
-        <v>0</v>
+        <v>-0.06854316592216492</v>
       </c>
     </row>
   </sheetData>
